--- a/templates/excel/format CC1.xlsx
+++ b/templates/excel/format CC1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CA-DEV\CA-BACKEND-DEV\templates\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{949E85DC-DECE-4002-B681-C4FC935E540D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336AB190-9470-4E9D-84BA-E647A9F15DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions.1" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="301">
   <si>
     <t>Sections</t>
   </si>
@@ -97,9 +97,6 @@
     <t>Soleproprietorship,Partnership,LLP,Company</t>
   </si>
   <si>
-    <t>LLP</t>
-  </si>
-  <si>
     <t>Proprietor / MP / MD Name</t>
   </si>
   <si>
@@ -607,37 +604,7 @@
     <t>PROJECTIONS AND ESTIMATIONS</t>
   </si>
   <si>
-    <t>Please use "IF" function in following cases</t>
-  </si>
-  <si>
     <t>OF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In case of </t>
-  </si>
-  <si>
-    <t>Designation</t>
-  </si>
-  <si>
-    <t>Companies</t>
-  </si>
-  <si>
-    <t>Managing Director</t>
-  </si>
-  <si>
-    <t>Designated Partner</t>
-  </si>
-  <si>
-    <t>Soleproprietor</t>
-  </si>
-  <si>
-    <t>Proprietor</t>
-  </si>
-  <si>
-    <t>Partnership firm</t>
-  </si>
-  <si>
-    <t>Managing Partner</t>
   </si>
   <si>
     <t xml:space="preserve">Working (CC) Capital Loan </t>
@@ -2069,7 +2036,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="400">
+  <cellXfs count="380">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2563,8 +2530,6 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2696,66 +2661,25 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="23" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2764,9 +2688,83 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="23" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2774,30 +2772,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2806,9 +2796,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2858,64 +2845,8 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4400,10 +4331,10 @@
       <c r="H3" s="112" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="315" t="s">
+      <c r="I3" s="318" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="316"/>
+      <c r="J3" s="319"/>
       <c r="L3" s="91"/>
       <c r="M3" s="123"/>
       <c r="N3" s="123"/>
@@ -4412,7 +4343,7 @@
       <c r="Q3" s="123"/>
     </row>
     <row r="4" spans="2:17" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="333" t="s">
+      <c r="B4" s="308" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="173" t="s">
@@ -4437,7 +4368,7 @@
       <c r="Q4" s="123"/>
     </row>
     <row r="5" spans="2:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="308"/>
+      <c r="B5" s="309"/>
       <c r="C5" s="210" t="s">
         <v>12</v>
       </c>
@@ -4452,7 +4383,7 @@
       </c>
       <c r="G5" s="201"/>
       <c r="H5" s="132"/>
-      <c r="I5" s="245"/>
+      <c r="I5" s="243"/>
       <c r="J5" s="204"/>
       <c r="L5" s="91"/>
       <c r="M5" s="123"/>
@@ -4462,9 +4393,9 @@
       <c r="Q5" s="123"/>
     </row>
     <row r="6" spans="2:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="308"/>
+      <c r="B6" s="309"/>
       <c r="C6" s="177" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" s="178" t="s">
         <v>10</v>
@@ -4485,9 +4416,9 @@
       <c r="Q6" s="123"/>
     </row>
     <row r="7" spans="2:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="308"/>
+      <c r="B7" s="309"/>
       <c r="C7" s="181" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" s="182" t="s">
         <v>10</v>
@@ -4508,18 +4439,18 @@
       <c r="Q7" s="123"/>
     </row>
     <row r="8" spans="2:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="308"/>
+      <c r="B8" s="309"/>
       <c r="C8" s="184" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="183" t="s">
         <v>18</v>
-      </c>
-      <c r="D8" s="183" t="s">
-        <v>19</v>
       </c>
       <c r="E8" s="185" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="178" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G8" s="184"/>
       <c r="H8" s="127"/>
@@ -4533,9 +4464,9 @@
       <c r="Q8" s="123"/>
     </row>
     <row r="9" spans="2:17" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="334"/>
+      <c r="B9" s="310"/>
       <c r="C9" s="187" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D9" s="188" t="s">
         <v>10</v>
@@ -4573,20 +4504,20 @@
       <c r="Q10" s="123"/>
     </row>
     <row r="11" spans="2:17" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="310" t="s">
+      <c r="B11" s="317" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="174" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="174" t="s">
+      <c r="D11" s="190" t="s">
         <v>23</v>
-      </c>
-      <c r="D11" s="190" t="s">
-        <v>24</v>
       </c>
       <c r="E11" s="175" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="175" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G11" s="175"/>
       <c r="H11" s="113"/>
@@ -4600,22 +4531,22 @@
       <c r="Q11" s="123"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B12" s="311"/>
+      <c r="B12" s="315"/>
       <c r="C12" s="173" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D12" s="174" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="175" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F12" s="174"/>
       <c r="G12" s="174"/>
       <c r="H12" s="113"/>
       <c r="I12" s="192"/>
       <c r="J12" s="164" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L12" s="91"/>
       <c r="M12" s="123"/>
@@ -4625,15 +4556,15 @@
       <c r="Q12" s="123"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B13" s="311"/>
+      <c r="B13" s="315"/>
       <c r="C13" s="177" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D13" s="178" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F13" s="178"/>
       <c r="G13" s="178"/>
@@ -4643,7 +4574,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="165" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K13" s="91">
         <f>12%</f>
@@ -4656,15 +4587,15 @@
       <c r="Q13" s="123"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B14" s="311"/>
+      <c r="B14" s="315"/>
       <c r="C14" s="177" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D14" s="178" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F14" s="178"/>
       <c r="G14" s="178"/>
@@ -4686,19 +4617,19 @@
       <c r="Q14" s="123"/>
     </row>
     <row r="15" spans="2:17" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="312"/>
+      <c r="B15" s="316"/>
       <c r="C15" s="177" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D15" s="178" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F15" s="178"/>
       <c r="G15" s="185" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H15" s="226"/>
       <c r="I15" s="228">
@@ -4706,7 +4637,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="165" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K15" s="225">
         <f>20%</f>
@@ -4737,26 +4668,26 @@
       <c r="Q16" s="123"/>
     </row>
     <row r="17" spans="1:18" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="310" t="s">
+      <c r="B17" s="317" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="178" t="s">
         <v>35</v>
-      </c>
-      <c r="C17" s="178" t="s">
-        <v>36</v>
       </c>
       <c r="D17" s="178" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F17" s="174" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G17" s="178"/>
       <c r="H17" s="90"/>
       <c r="I17" s="179"/>
       <c r="J17" s="166" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L17" s="91"/>
       <c r="M17" s="123"/>
@@ -4766,24 +4697,24 @@
       <c r="Q17" s="123"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="311"/>
+      <c r="B18" s="315"/>
       <c r="C18" s="178" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D18" s="178" t="s">
         <v>13</v>
       </c>
       <c r="E18" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F18" s="174" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G18" s="178"/>
       <c r="H18" s="90"/>
       <c r="I18" s="179"/>
       <c r="J18" s="166" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L18" s="91"/>
       <c r="M18" s="123"/>
@@ -4793,24 +4724,24 @@
       <c r="Q18" s="123"/>
     </row>
     <row r="19" spans="1:18" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="311"/>
+      <c r="B19" s="315"/>
       <c r="C19" s="178" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D19" s="178" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F19" s="174" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G19" s="178"/>
       <c r="H19" s="90"/>
       <c r="I19" s="179"/>
       <c r="J19" s="166" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L19" s="91"/>
       <c r="M19" s="123"/>
@@ -4820,24 +4751,24 @@
       <c r="Q19" s="123"/>
     </row>
     <row r="20" spans="1:18" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="311"/>
+      <c r="B20" s="315"/>
       <c r="C20" s="178" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D20" s="178" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F20" s="174" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G20" s="178"/>
       <c r="H20" s="90"/>
       <c r="I20" s="179"/>
       <c r="J20" s="166" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L20" s="91"/>
       <c r="M20" s="123"/>
@@ -4847,24 +4778,24 @@
       <c r="Q20" s="123"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B21" s="312"/>
+      <c r="B21" s="316"/>
       <c r="C21" s="178" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D21" s="178" t="s">
         <v>13</v>
       </c>
       <c r="E21" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F21" s="174" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G21" s="178"/>
       <c r="H21" s="90"/>
       <c r="I21" s="179"/>
       <c r="J21" s="166" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L21" s="91"/>
       <c r="M21" s="123"/>
@@ -4882,10 +4813,10 @@
       <c r="G22" s="193"/>
       <c r="H22" s="129"/>
       <c r="I22" s="170" t="s">
+        <v>43</v>
+      </c>
+      <c r="J22" s="171" t="s">
         <v>44</v>
-      </c>
-      <c r="J22" s="171" t="s">
-        <v>45</v>
       </c>
       <c r="M22" s="123"/>
       <c r="N22" s="123"/>
@@ -4895,17 +4826,17 @@
       <c r="R22" s="91"/>
     </row>
     <row r="23" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="310" t="s">
+      <c r="B23" s="317" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="178" t="s">
         <v>46</v>
-      </c>
-      <c r="C23" s="178" t="s">
-        <v>47</v>
       </c>
       <c r="D23" s="178" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F23" s="178"/>
       <c r="G23" s="178"/>
@@ -4920,15 +4851,15 @@
       <c r="R23" s="91"/>
     </row>
     <row r="24" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="311"/>
+      <c r="B24" s="315"/>
       <c r="C24" s="178" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D24" s="178" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F24" s="178"/>
       <c r="G24" s="178"/>
@@ -4943,18 +4874,18 @@
       <c r="R24" s="91"/>
     </row>
     <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="329" t="s">
+      <c r="A25" s="303" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="316"/>
+      <c r="C25" s="178" t="s">
         <v>49</v>
-      </c>
-      <c r="B25" s="312"/>
-      <c r="C25" s="178" t="s">
-        <v>50</v>
       </c>
       <c r="D25" s="178" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F25" s="178"/>
       <c r="G25" s="178"/>
@@ -4969,7 +4900,7 @@
       <c r="R25" s="91"/>
     </row>
     <row r="26" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="319"/>
+      <c r="A26" s="304"/>
       <c r="B26" s="125"/>
       <c r="C26" s="195"/>
       <c r="D26" s="196"/>
@@ -4987,17 +4918,17 @@
       <c r="R26" s="91"/>
     </row>
     <row r="27" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="313" t="s">
+      <c r="B27" s="338" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="198" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="198" t="s">
+      <c r="D27" s="174" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="174" t="s">
+      <c r="E27" s="175" t="s">
         <v>53</v>
-      </c>
-      <c r="E27" s="175" t="s">
-        <v>54</v>
       </c>
       <c r="F27" s="174"/>
       <c r="G27" s="174"/>
@@ -5015,15 +4946,15 @@
       <c r="R27" s="91"/>
     </row>
     <row r="28" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="308"/>
+      <c r="B28" s="309"/>
       <c r="C28" s="199" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D28" s="178" t="s">
         <v>10</v>
       </c>
       <c r="E28" s="148" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F28" s="178"/>
       <c r="G28" s="178"/>
@@ -5033,7 +4964,7 @@
         <v>1</v>
       </c>
       <c r="J28" s="209" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K28" s="225"/>
       <c r="M28" s="123"/>
@@ -5044,35 +4975,35 @@
       <c r="R28" s="91"/>
     </row>
     <row r="29" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="308"/>
+      <c r="B29" s="309"/>
       <c r="C29" s="200" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D29" s="201" t="s">
         <v>10</v>
       </c>
       <c r="E29" s="202" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F29" s="201"/>
       <c r="G29" s="201"/>
       <c r="H29" s="132"/>
       <c r="I29" s="203"/>
       <c r="J29" s="204" t="s">
+        <v>57</v>
+      </c>
+      <c r="R29" s="91"/>
+    </row>
+    <row r="30" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="309"/>
+      <c r="C30" s="199" t="s">
         <v>58</v>
-      </c>
-      <c r="R29" s="91"/>
-    </row>
-    <row r="30" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="308"/>
-      <c r="C30" s="199" t="s">
-        <v>59</v>
       </c>
       <c r="D30" s="178" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F30" s="178"/>
       <c r="G30" s="178"/>
@@ -5082,47 +5013,47 @@
         <v>1</v>
       </c>
       <c r="J30" s="180" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L30" s="91"/>
       <c r="R30" s="91"/>
     </row>
     <row r="31" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="308"/>
+      <c r="B31" s="309"/>
       <c r="C31" s="199" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D31" s="178" t="s">
         <v>10</v>
       </c>
       <c r="E31" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F31" s="178"/>
       <c r="G31" s="178"/>
       <c r="H31" s="90"/>
       <c r="I31" s="205"/>
       <c r="J31" s="180" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K31" s="85"/>
       <c r="L31" s="91"/>
-      <c r="M31" s="303"/>
-      <c r="N31" s="304"/>
-      <c r="O31" s="304"/>
-      <c r="P31" s="304"/>
-      <c r="Q31" s="304"/>
+      <c r="M31" s="336"/>
+      <c r="N31" s="337"/>
+      <c r="O31" s="337"/>
+      <c r="P31" s="337"/>
+      <c r="Q31" s="337"/>
     </row>
     <row r="32" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="308"/>
+      <c r="B32" s="309"/>
       <c r="C32" s="199" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D32" s="178" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F32" s="178"/>
       <c r="G32" s="178"/>
@@ -5132,7 +5063,7 @@
         <v>1</v>
       </c>
       <c r="J32" s="180" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K32" s="85"/>
       <c r="L32" s="91"/>
@@ -5143,15 +5074,15 @@
       <c r="Q32" s="123"/>
     </row>
     <row r="33" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="308"/>
+      <c r="B33" s="309"/>
       <c r="C33" s="206" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D33" s="207" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="208" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F33" s="207"/>
       <c r="G33" s="207"/>
@@ -5161,7 +5092,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="209" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K33" s="85"/>
       <c r="L33" s="91"/>
@@ -5172,22 +5103,22 @@
       <c r="Q33" s="123"/>
     </row>
     <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="308"/>
+      <c r="B34" s="309"/>
       <c r="C34" s="210" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D34" s="201" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="202" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F34" s="201"/>
       <c r="G34" s="201"/>
       <c r="H34" s="124"/>
       <c r="I34" s="211"/>
       <c r="J34" s="212" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K34" s="85"/>
       <c r="L34" s="91"/>
@@ -5198,22 +5129,22 @@
       <c r="Q34" s="123"/>
     </row>
     <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="308"/>
+      <c r="B35" s="309"/>
       <c r="C35" s="177" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D35" s="178" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F35" s="178"/>
       <c r="G35" s="178"/>
       <c r="H35" s="127"/>
       <c r="I35" s="205"/>
       <c r="J35" s="213" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K35" s="85"/>
       <c r="L35" s="91"/>
@@ -5230,49 +5161,49 @@
       <c r="D36" s="189"/>
       <c r="E36" s="189"/>
       <c r="F36" s="155" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G36" s="189"/>
       <c r="H36" s="135"/>
-      <c r="I36" s="292" t="s">
+      <c r="I36" s="290" t="s">
+        <v>68</v>
+      </c>
+      <c r="J36" s="214"/>
+    </row>
+    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="317" t="s">
         <v>69</v>
       </c>
-      <c r="J36" s="214"/>
-    </row>
-    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="310" t="s">
+      <c r="C37" s="178" t="s">
         <v>70</v>
-      </c>
-      <c r="C37" s="178" t="s">
-        <v>71</v>
       </c>
       <c r="D37" s="178" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F37" s="241">
         <v>0.15</v>
       </c>
       <c r="G37" s="178"/>
       <c r="H37" s="215"/>
-      <c r="I37" s="293">
+      <c r="I37" s="291">
         <f>F99</f>
         <v>0</v>
       </c>
       <c r="J37" s="213"/>
     </row>
     <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="311"/>
+      <c r="B38" s="315"/>
       <c r="C38" s="178" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D38" s="178" t="s">
         <v>10</v>
       </c>
       <c r="E38" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F38" s="241">
         <v>0.15</v>
@@ -5286,15 +5217,15 @@
       <c r="J38" s="212"/>
     </row>
     <row r="39" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="311"/>
+      <c r="B39" s="315"/>
       <c r="C39" s="178" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D39" s="178" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F39" s="241">
         <v>0.1</v>
@@ -5308,15 +5239,15 @@
       <c r="J39" s="212"/>
     </row>
     <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="311"/>
+      <c r="B40" s="315"/>
       <c r="C40" s="178" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D40" s="178" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F40" s="241">
         <v>0</v>
@@ -5330,15 +5261,15 @@
       <c r="J40" s="212"/>
     </row>
     <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="311"/>
+      <c r="B41" s="315"/>
       <c r="C41" s="178" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D41" s="178" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F41" s="241">
         <v>0.15</v>
@@ -5352,15 +5283,15 @@
       <c r="J41" s="212"/>
     </row>
     <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="311"/>
+      <c r="B42" s="315"/>
       <c r="C42" s="178" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D42" s="178" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F42" s="241">
         <v>0.15</v>
@@ -5375,15 +5306,15 @@
     </row>
     <row r="43" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="115"/>
-      <c r="B43" s="311"/>
+      <c r="B43" s="315"/>
       <c r="C43" s="178" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D43" s="178" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F43" s="241">
         <v>0.15</v>
@@ -5397,15 +5328,15 @@
       <c r="J43" s="212"/>
     </row>
     <row r="44" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="311"/>
+      <c r="B44" s="315"/>
       <c r="C44" s="178" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D44" s="178" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F44" s="241">
         <v>0</v>
@@ -5419,15 +5350,15 @@
       <c r="J44" s="212"/>
     </row>
     <row r="45" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="311"/>
+      <c r="B45" s="315"/>
       <c r="C45" s="178" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D45" s="178" t="s">
         <v>10</v>
       </c>
       <c r="E45" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F45" s="241">
         <v>0</v>
@@ -5441,15 +5372,15 @@
       <c r="J45" s="212"/>
     </row>
     <row r="46" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="312"/>
+      <c r="B46" s="316"/>
       <c r="C46" s="178" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D46" s="178" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="179" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F46" s="241">
         <v>0.1</v>
@@ -5472,14 +5403,14 @@
       <c r="F49" s="131"/>
     </row>
     <row r="50" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="335" t="s">
-        <v>51</v>
+      <c r="B50" s="314" t="s">
+        <v>50</v>
       </c>
       <c r="C50" s="150" t="s">
-        <v>81</v>
-      </c>
-      <c r="D50" s="322"/>
-      <c r="E50" s="323"/>
+        <v>80</v>
+      </c>
+      <c r="D50" s="329"/>
+      <c r="E50" s="330"/>
       <c r="F50" s="193"/>
       <c r="G50" s="193"/>
       <c r="H50" s="129"/>
@@ -5494,19 +5425,19 @@
       <c r="Q50" s="123"/>
     </row>
     <row r="51" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="311"/>
+      <c r="B51" s="315"/>
       <c r="C51" s="220" t="s">
-        <v>36</v>
-      </c>
-      <c r="D51" s="325" t="s">
-        <v>82</v>
-      </c>
-      <c r="E51" s="326"/>
+        <v>35</v>
+      </c>
+      <c r="D51" s="332" t="s">
+        <v>81</v>
+      </c>
+      <c r="E51" s="333"/>
       <c r="F51" s="231">
         <v>0.05</v>
       </c>
       <c r="G51" s="221" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H51" s="143"/>
       <c r="I51" s="143"/>
@@ -5520,17 +5451,17 @@
       <c r="Q51" s="123"/>
     </row>
     <row r="52" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="311"/>
+      <c r="B52" s="315"/>
       <c r="C52" s="220" t="s">
-        <v>39</v>
-      </c>
-      <c r="D52" s="327"/>
-      <c r="E52" s="327"/>
+        <v>38</v>
+      </c>
+      <c r="D52" s="334"/>
+      <c r="E52" s="334"/>
       <c r="F52" s="230">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G52" s="221" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H52" s="143"/>
       <c r="I52" s="143"/>
@@ -5544,17 +5475,17 @@
       <c r="Q52" s="123"/>
     </row>
     <row r="53" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="311"/>
+      <c r="B53" s="315"/>
       <c r="C53" s="220" t="s">
-        <v>41</v>
-      </c>
-      <c r="D53" s="327"/>
-      <c r="E53" s="327"/>
+        <v>40</v>
+      </c>
+      <c r="D53" s="334"/>
+      <c r="E53" s="334"/>
       <c r="F53" s="230">
         <v>0.09</v>
       </c>
       <c r="G53" s="221" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H53" s="143"/>
       <c r="I53" s="143"/>
@@ -5568,17 +5499,17 @@
       <c r="Q53" s="123"/>
     </row>
     <row r="54" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="311"/>
+      <c r="B54" s="315"/>
       <c r="C54" s="220" t="s">
-        <v>42</v>
-      </c>
-      <c r="D54" s="327"/>
-      <c r="E54" s="327"/>
+        <v>41</v>
+      </c>
+      <c r="D54" s="334"/>
+      <c r="E54" s="334"/>
       <c r="F54" s="231">
         <v>0.11</v>
       </c>
       <c r="G54" s="221" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H54" s="143"/>
       <c r="I54" s="143"/>
@@ -5592,17 +5523,17 @@
       <c r="Q54" s="123"/>
     </row>
     <row r="55" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="311"/>
+      <c r="B55" s="315"/>
       <c r="C55" s="220" t="s">
-        <v>43</v>
-      </c>
-      <c r="D55" s="327"/>
-      <c r="E55" s="327"/>
+        <v>42</v>
+      </c>
+      <c r="D55" s="334"/>
+      <c r="E55" s="334"/>
       <c r="F55" s="230">
         <v>0.13</v>
       </c>
       <c r="G55" s="221" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H55" s="143"/>
       <c r="I55" s="143"/>
@@ -5616,12 +5547,12 @@
       <c r="Q55" s="123"/>
     </row>
     <row r="56" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="311"/>
+      <c r="B56" s="315"/>
       <c r="C56" s="150" t="s">
-        <v>84</v>
-      </c>
-      <c r="D56" s="327"/>
-      <c r="E56" s="327"/>
+        <v>83</v>
+      </c>
+      <c r="D56" s="334"/>
+      <c r="E56" s="334"/>
       <c r="F56" s="232"/>
       <c r="G56" s="193"/>
       <c r="H56" s="129"/>
@@ -5636,17 +5567,17 @@
       <c r="Q56" s="123"/>
     </row>
     <row r="57" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="311"/>
+      <c r="B57" s="315"/>
       <c r="C57" s="220" t="s">
-        <v>36</v>
-      </c>
-      <c r="D57" s="327"/>
-      <c r="E57" s="327"/>
+        <v>35</v>
+      </c>
+      <c r="D57" s="334"/>
+      <c r="E57" s="334"/>
       <c r="F57" s="233">
         <v>0.25</v>
       </c>
       <c r="G57" s="221" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H57" s="143"/>
       <c r="I57" s="143"/>
@@ -5660,17 +5591,17 @@
       <c r="Q57" s="123"/>
     </row>
     <row r="58" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="311"/>
+      <c r="B58" s="315"/>
       <c r="C58" s="220" t="s">
-        <v>39</v>
-      </c>
-      <c r="D58" s="327"/>
-      <c r="E58" s="327"/>
+        <v>38</v>
+      </c>
+      <c r="D58" s="334"/>
+      <c r="E58" s="334"/>
       <c r="F58" s="234">
         <v>0.25</v>
       </c>
       <c r="G58" s="221" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H58" s="143"/>
       <c r="I58" s="143"/>
@@ -5684,17 +5615,17 @@
       <c r="Q58" s="123"/>
     </row>
     <row r="59" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="311"/>
+      <c r="B59" s="315"/>
       <c r="C59" s="220" t="s">
-        <v>41</v>
-      </c>
-      <c r="D59" s="327"/>
-      <c r="E59" s="327"/>
+        <v>40</v>
+      </c>
+      <c r="D59" s="334"/>
+      <c r="E59" s="334"/>
       <c r="F59" s="234">
         <v>0.25</v>
       </c>
       <c r="G59" s="221" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H59" s="143"/>
       <c r="I59" s="143"/>
@@ -5708,17 +5639,17 @@
       <c r="Q59" s="123"/>
     </row>
     <row r="60" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="311"/>
+      <c r="B60" s="315"/>
       <c r="C60" s="220" t="s">
-        <v>42</v>
-      </c>
-      <c r="D60" s="327"/>
-      <c r="E60" s="327"/>
+        <v>41</v>
+      </c>
+      <c r="D60" s="334"/>
+      <c r="E60" s="334"/>
       <c r="F60" s="230">
         <v>0.25</v>
       </c>
       <c r="G60" s="221" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H60" s="143"/>
       <c r="I60" s="143"/>
@@ -5732,17 +5663,17 @@
       <c r="Q60" s="123"/>
     </row>
     <row r="61" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="311"/>
+      <c r="B61" s="315"/>
       <c r="C61" s="220" t="s">
-        <v>43</v>
-      </c>
-      <c r="D61" s="327"/>
-      <c r="E61" s="327"/>
+        <v>42</v>
+      </c>
+      <c r="D61" s="334"/>
+      <c r="E61" s="334"/>
       <c r="F61" s="230">
         <v>0.25</v>
       </c>
       <c r="G61" s="221" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H61" s="143"/>
       <c r="I61" s="143"/>
@@ -5756,12 +5687,12 @@
       <c r="Q61" s="123"/>
     </row>
     <row r="62" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="311"/>
+      <c r="B62" s="315"/>
       <c r="C62" s="150" t="s">
-        <v>86</v>
-      </c>
-      <c r="D62" s="327"/>
-      <c r="E62" s="327"/>
+        <v>85</v>
+      </c>
+      <c r="D62" s="334"/>
+      <c r="E62" s="334"/>
       <c r="F62" s="232"/>
       <c r="G62" s="193"/>
       <c r="H62" s="129"/>
@@ -5776,19 +5707,19 @@
       <c r="Q62" s="123"/>
     </row>
     <row r="63" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="311"/>
+      <c r="B63" s="315"/>
       <c r="C63" s="220" t="s">
-        <v>36</v>
-      </c>
-      <c r="D63" s="327"/>
-      <c r="E63" s="327"/>
+        <v>35</v>
+      </c>
+      <c r="D63" s="334"/>
+      <c r="E63" s="334"/>
       <c r="F63" s="230">
         <v>0.1</v>
       </c>
       <c r="G63" s="221" t="s">
-        <v>85</v>
-      </c>
-      <c r="H63" s="251" t="e">
+        <v>84</v>
+      </c>
+      <c r="H63" s="249" t="e">
         <f>wc!C83</f>
         <v>#DIV/0!</v>
       </c>
@@ -5803,19 +5734,19 @@
       <c r="Q63" s="123"/>
     </row>
     <row r="64" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="311"/>
+      <c r="B64" s="315"/>
       <c r="C64" s="220" t="s">
-        <v>39</v>
-      </c>
-      <c r="D64" s="327"/>
-      <c r="E64" s="327"/>
+        <v>38</v>
+      </c>
+      <c r="D64" s="334"/>
+      <c r="E64" s="334"/>
       <c r="F64" s="230">
         <v>0.12</v>
       </c>
       <c r="G64" s="221" t="s">
-        <v>85</v>
-      </c>
-      <c r="H64" s="251" t="e">
+        <v>84</v>
+      </c>
+      <c r="H64" s="249" t="e">
         <f>wc!D83</f>
         <v>#DIV/0!</v>
       </c>
@@ -5830,19 +5761,19 @@
       <c r="Q64" s="123"/>
     </row>
     <row r="65" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="311"/>
+      <c r="B65" s="315"/>
       <c r="C65" s="220" t="s">
-        <v>41</v>
-      </c>
-      <c r="D65" s="327"/>
-      <c r="E65" s="327"/>
+        <v>40</v>
+      </c>
+      <c r="D65" s="334"/>
+      <c r="E65" s="334"/>
       <c r="F65" s="230">
         <v>0.14000000000000001</v>
       </c>
       <c r="G65" s="221" t="s">
-        <v>85</v>
-      </c>
-      <c r="H65" s="251" t="e">
+        <v>84</v>
+      </c>
+      <c r="H65" s="249" t="e">
         <f>wc!E83</f>
         <v>#DIV/0!</v>
       </c>
@@ -5857,19 +5788,19 @@
       <c r="Q65" s="123"/>
     </row>
     <row r="66" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="311"/>
+      <c r="B66" s="315"/>
       <c r="C66" s="220" t="s">
-        <v>42</v>
-      </c>
-      <c r="D66" s="327"/>
-      <c r="E66" s="327"/>
+        <v>41</v>
+      </c>
+      <c r="D66" s="334"/>
+      <c r="E66" s="334"/>
       <c r="F66" s="230">
         <v>0.16</v>
       </c>
       <c r="G66" s="221" t="s">
-        <v>85</v>
-      </c>
-      <c r="H66" s="251" t="e">
+        <v>84</v>
+      </c>
+      <c r="H66" s="249" t="e">
         <f>wc!F83</f>
         <v>#DIV/0!</v>
       </c>
@@ -5884,19 +5815,19 @@
       <c r="Q66" s="123"/>
     </row>
     <row r="67" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="311"/>
+      <c r="B67" s="315"/>
       <c r="C67" s="220" t="s">
-        <v>43</v>
-      </c>
-      <c r="D67" s="327"/>
-      <c r="E67" s="327"/>
+        <v>42</v>
+      </c>
+      <c r="D67" s="334"/>
+      <c r="E67" s="334"/>
       <c r="F67" s="230">
         <v>0.18</v>
       </c>
       <c r="G67" s="221" t="s">
-        <v>85</v>
-      </c>
-      <c r="H67" s="251" t="e">
+        <v>84</v>
+      </c>
+      <c r="H67" s="249" t="e">
         <f>wc!G83</f>
         <v>#DIV/0!</v>
       </c>
@@ -5911,12 +5842,12 @@
       <c r="Q67" s="123"/>
     </row>
     <row r="68" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B68" s="311"/>
+      <c r="B68" s="315"/>
       <c r="C68" s="151" t="s">
-        <v>87</v>
-      </c>
-      <c r="D68" s="327"/>
-      <c r="E68" s="327"/>
+        <v>86</v>
+      </c>
+      <c r="D68" s="334"/>
+      <c r="E68" s="334"/>
       <c r="F68" s="235"/>
       <c r="G68" s="223"/>
       <c r="H68" s="152"/>
@@ -5925,69 +5856,69 @@
       <c r="K68" s="85"/>
     </row>
     <row r="69" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="311"/>
+      <c r="B69" s="315"/>
       <c r="C69" s="220" t="s">
-        <v>88</v>
-      </c>
-      <c r="D69" s="327"/>
-      <c r="E69" s="327"/>
+        <v>87</v>
+      </c>
+      <c r="D69" s="334"/>
+      <c r="E69" s="334"/>
       <c r="F69" s="230">
         <v>12</v>
       </c>
       <c r="G69" s="222" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H69" s="143"/>
       <c r="I69" s="143"/>
       <c r="J69" s="144"/>
     </row>
     <row r="70" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="311"/>
+      <c r="B70" s="315"/>
       <c r="C70" s="220" t="s">
-        <v>89</v>
-      </c>
-      <c r="D70" s="327"/>
-      <c r="E70" s="327"/>
+        <v>88</v>
+      </c>
+      <c r="D70" s="334"/>
+      <c r="E70" s="334"/>
       <c r="F70" s="230">
         <v>1.0049999999999999</v>
       </c>
       <c r="G70" s="222" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H70" s="145"/>
       <c r="I70" s="145"/>
       <c r="J70" s="144"/>
     </row>
     <row r="71" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="311"/>
+      <c r="B71" s="315"/>
       <c r="C71" s="220" t="s">
-        <v>91</v>
-      </c>
-      <c r="D71" s="327"/>
-      <c r="E71" s="327"/>
+        <v>90</v>
+      </c>
+      <c r="D71" s="334"/>
+      <c r="E71" s="334"/>
       <c r="F71" s="230" t="e">
         <f>100/I15/100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G71" s="222" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H71" s="143"/>
       <c r="I71" s="143"/>
       <c r="J71" s="144"/>
     </row>
     <row r="72" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="311"/>
+      <c r="B72" s="315"/>
       <c r="C72" s="220" t="s">
-        <v>93</v>
-      </c>
-      <c r="D72" s="327"/>
-      <c r="E72" s="327"/>
+        <v>92</v>
+      </c>
+      <c r="D72" s="334"/>
+      <c r="E72" s="334"/>
       <c r="F72" s="230">
         <v>0.01</v>
       </c>
       <c r="G72" s="222" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H72" s="143"/>
       <c r="I72" s="143"/>
@@ -5995,17 +5926,17 @@
       <c r="R72" s="103"/>
     </row>
     <row r="73" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="311"/>
+      <c r="B73" s="315"/>
       <c r="C73" s="220" t="s">
-        <v>95</v>
-      </c>
-      <c r="D73" s="327"/>
-      <c r="E73" s="327"/>
+        <v>94</v>
+      </c>
+      <c r="D73" s="334"/>
+      <c r="E73" s="334"/>
       <c r="F73" s="230">
         <v>1.05</v>
       </c>
       <c r="G73" s="222" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H73" s="143"/>
       <c r="I73" s="143"/>
@@ -6013,17 +5944,17 @@
       <c r="R73" s="91"/>
     </row>
     <row r="74" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="311"/>
+      <c r="B74" s="315"/>
       <c r="C74" s="220" t="s">
-        <v>96</v>
-      </c>
-      <c r="D74" s="327"/>
-      <c r="E74" s="327"/>
+        <v>95</v>
+      </c>
+      <c r="D74" s="334"/>
+      <c r="E74" s="334"/>
       <c r="F74" s="230">
         <v>0.5</v>
       </c>
       <c r="G74" s="144" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H74" s="143"/>
       <c r="I74" s="143"/>
@@ -6031,46 +5962,46 @@
       <c r="R74" s="91"/>
     </row>
     <row r="75" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="311"/>
+      <c r="B75" s="315"/>
       <c r="C75" s="220" t="s">
-        <v>98</v>
-      </c>
-      <c r="D75" s="327"/>
-      <c r="E75" s="327"/>
+        <v>97</v>
+      </c>
+      <c r="D75" s="334"/>
+      <c r="E75" s="334"/>
       <c r="F75" s="230">
         <v>0.01</v>
       </c>
       <c r="G75" s="144" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H75" s="143"/>
       <c r="I75" s="143"/>
       <c r="J75" s="144"/>
     </row>
     <row r="76" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="311"/>
+      <c r="B76" s="315"/>
       <c r="C76" s="220" t="s">
-        <v>100</v>
-      </c>
-      <c r="D76" s="327"/>
-      <c r="E76" s="327"/>
+        <v>99</v>
+      </c>
+      <c r="D76" s="334"/>
+      <c r="E76" s="334"/>
       <c r="F76" s="230">
         <v>0.2</v>
       </c>
       <c r="G76" s="222" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H76" s="143"/>
       <c r="I76" s="143"/>
       <c r="J76" s="144"/>
     </row>
     <row r="77" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="311"/>
+      <c r="B77" s="315"/>
       <c r="C77" s="220" t="s">
-        <v>101</v>
-      </c>
-      <c r="D77" s="327"/>
-      <c r="E77" s="327"/>
+        <v>100</v>
+      </c>
+      <c r="D77" s="334"/>
+      <c r="E77" s="334"/>
       <c r="F77" s="230">
         <v>0</v>
       </c>
@@ -6080,34 +6011,34 @@
       <c r="J77" s="144"/>
     </row>
     <row r="78" spans="2:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="311"/>
+      <c r="B78" s="315"/>
       <c r="C78" s="220" t="s">
-        <v>102</v>
-      </c>
-      <c r="D78" s="327"/>
-      <c r="E78" s="327"/>
+        <v>101</v>
+      </c>
+      <c r="D78" s="334"/>
+      <c r="E78" s="334"/>
       <c r="F78" s="230">
         <v>0.9</v>
       </c>
       <c r="G78" s="222" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H78" s="143"/>
       <c r="I78" s="143"/>
       <c r="J78" s="144"/>
     </row>
     <row r="79" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="311"/>
+      <c r="B79" s="315"/>
       <c r="C79" s="220" t="s">
-        <v>103</v>
-      </c>
-      <c r="D79" s="327"/>
-      <c r="E79" s="327"/>
+        <v>102</v>
+      </c>
+      <c r="D79" s="334"/>
+      <c r="E79" s="334"/>
       <c r="F79" s="230">
         <v>1.3</v>
       </c>
       <c r="G79" s="222" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H79" s="143"/>
       <c r="I79" s="143"/>
@@ -6115,17 +6046,17 @@
       <c r="Q79" s="218"/>
     </row>
     <row r="80" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="311"/>
+      <c r="B80" s="315"/>
       <c r="C80" s="220" t="s">
-        <v>104</v>
-      </c>
-      <c r="D80" s="327"/>
-      <c r="E80" s="327"/>
+        <v>103</v>
+      </c>
+      <c r="D80" s="334"/>
+      <c r="E80" s="334"/>
       <c r="F80" s="230">
         <v>1.01</v>
       </c>
       <c r="G80" s="222" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H80" s="143"/>
       <c r="I80" s="143"/>
@@ -6133,12 +6064,12 @@
       <c r="Q80" s="218"/>
     </row>
     <row r="81" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="311"/>
+      <c r="B81" s="315"/>
       <c r="C81" s="150" t="s">
-        <v>106</v>
-      </c>
-      <c r="D81" s="327"/>
-      <c r="E81" s="327"/>
+        <v>105</v>
+      </c>
+      <c r="D81" s="334"/>
+      <c r="E81" s="334"/>
       <c r="F81" s="236"/>
       <c r="G81" s="193"/>
       <c r="H81" s="129"/>
@@ -6147,12 +6078,12 @@
       <c r="Q81" s="218"/>
     </row>
     <row r="82" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B82" s="311"/>
+      <c r="B82" s="315"/>
       <c r="C82" s="142" t="s">
-        <v>71</v>
-      </c>
-      <c r="D82" s="327"/>
-      <c r="E82" s="327"/>
+        <v>70</v>
+      </c>
+      <c r="D82" s="334"/>
+      <c r="E82" s="334"/>
       <c r="F82" s="230">
         <v>0.15</v>
       </c>
@@ -6163,12 +6094,12 @@
       <c r="Q82" s="218"/>
     </row>
     <row r="83" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="311"/>
+      <c r="B83" s="315"/>
       <c r="C83" s="142" t="s">
-        <v>72</v>
-      </c>
-      <c r="D83" s="327"/>
-      <c r="E83" s="327"/>
+        <v>71</v>
+      </c>
+      <c r="D83" s="334"/>
+      <c r="E83" s="334"/>
       <c r="F83" s="230">
         <v>0.15</v>
       </c>
@@ -6179,12 +6110,12 @@
       <c r="Q83" s="218"/>
     </row>
     <row r="84" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="311"/>
+      <c r="B84" s="315"/>
       <c r="C84" s="142" t="s">
-        <v>107</v>
-      </c>
-      <c r="D84" s="327"/>
-      <c r="E84" s="327"/>
+        <v>106</v>
+      </c>
+      <c r="D84" s="334"/>
+      <c r="E84" s="334"/>
       <c r="F84" s="230">
         <v>0.1</v>
       </c>
@@ -6195,12 +6126,12 @@
       <c r="Q84" s="218"/>
     </row>
     <row r="85" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="311"/>
+      <c r="B85" s="315"/>
       <c r="C85" s="142" t="s">
-        <v>74</v>
-      </c>
-      <c r="D85" s="327"/>
-      <c r="E85" s="327"/>
+        <v>73</v>
+      </c>
+      <c r="D85" s="334"/>
+      <c r="E85" s="334"/>
       <c r="F85" s="230">
         <v>0</v>
       </c>
@@ -6210,12 +6141,12 @@
       <c r="J85" s="144"/>
     </row>
     <row r="86" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B86" s="311"/>
+      <c r="B86" s="315"/>
       <c r="C86" s="142" t="s">
-        <v>75</v>
-      </c>
-      <c r="D86" s="327"/>
-      <c r="E86" s="327"/>
+        <v>74</v>
+      </c>
+      <c r="D86" s="334"/>
+      <c r="E86" s="334"/>
       <c r="F86" s="230">
         <v>0.15</v>
       </c>
@@ -6225,12 +6156,12 @@
       <c r="J86" s="144"/>
     </row>
     <row r="87" spans="2:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B87" s="311"/>
+      <c r="B87" s="315"/>
       <c r="C87" s="142" t="s">
-        <v>108</v>
-      </c>
-      <c r="D87" s="327"/>
-      <c r="E87" s="327"/>
+        <v>107</v>
+      </c>
+      <c r="D87" s="334"/>
+      <c r="E87" s="334"/>
       <c r="F87" s="230">
         <v>0.15</v>
       </c>
@@ -6241,12 +6172,12 @@
       <c r="N87" s="36"/>
     </row>
     <row r="88" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B88" s="311"/>
+      <c r="B88" s="315"/>
       <c r="C88" s="142" t="s">
-        <v>109</v>
-      </c>
-      <c r="D88" s="327"/>
-      <c r="E88" s="327"/>
+        <v>108</v>
+      </c>
+      <c r="D88" s="334"/>
+      <c r="E88" s="334"/>
       <c r="F88" s="230">
         <v>0.1</v>
       </c>
@@ -6256,12 +6187,12 @@
       <c r="J88" s="144"/>
     </row>
     <row r="89" spans="2:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B89" s="311"/>
+      <c r="B89" s="315"/>
       <c r="C89" s="142" t="s">
-        <v>77</v>
-      </c>
-      <c r="D89" s="327"/>
-      <c r="E89" s="327"/>
+        <v>76</v>
+      </c>
+      <c r="D89" s="334"/>
+      <c r="E89" s="334"/>
       <c r="F89" s="230">
         <v>0.15</v>
       </c>
@@ -6271,12 +6202,12 @@
       <c r="J89" s="144"/>
     </row>
     <row r="90" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B90" s="311"/>
+      <c r="B90" s="315"/>
       <c r="C90" s="142" t="s">
-        <v>110</v>
-      </c>
-      <c r="D90" s="327"/>
-      <c r="E90" s="327"/>
+        <v>109</v>
+      </c>
+      <c r="D90" s="334"/>
+      <c r="E90" s="334"/>
       <c r="F90" s="237">
         <v>0</v>
       </c>
@@ -6287,12 +6218,12 @@
       <c r="P90" s="104"/>
     </row>
     <row r="91" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B91" s="311"/>
+      <c r="B91" s="315"/>
       <c r="C91" s="142" t="s">
-        <v>79</v>
-      </c>
-      <c r="D91" s="327"/>
-      <c r="E91" s="327"/>
+        <v>78</v>
+      </c>
+      <c r="D91" s="334"/>
+      <c r="E91" s="334"/>
       <c r="F91" s="237">
         <v>0.1</v>
       </c>
@@ -6303,13 +6234,13 @@
       <c r="P91" s="104"/>
     </row>
     <row r="92" spans="2:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B92" s="312"/>
+      <c r="B92" s="316"/>
       <c r="C92" s="142" t="s">
-        <v>111</v>
-      </c>
-      <c r="D92" s="328"/>
-      <c r="E92" s="328"/>
-      <c r="F92" s="296">
+        <v>110</v>
+      </c>
+      <c r="D92" s="335"/>
+      <c r="E92" s="335"/>
+      <c r="F92" s="294">
         <v>0</v>
       </c>
       <c r="G92" s="221"/>
@@ -6318,1002 +6249,1002 @@
       <c r="J92" s="144"/>
     </row>
     <row r="97" spans="2:6" ht="22.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B97" s="254" t="s">
+      <c r="B97" s="252" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="98" spans="2:6" ht="26.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B98" s="253" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="98" spans="2:6" ht="26.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="255" t="s">
+      <c r="C98" s="254" t="s">
         <v>113</v>
       </c>
-      <c r="C98" s="256" t="s">
+      <c r="D98" s="253" t="s">
         <v>114</v>
       </c>
-      <c r="D98" s="255" t="s">
+      <c r="E98" s="255" t="s">
         <v>115</v>
       </c>
-      <c r="E98" s="257" t="s">
+      <c r="F98" s="255" t="s">
         <v>116</v>
       </c>
-      <c r="F98" s="257" t="s">
+    </row>
+    <row r="99" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B99" s="311" t="s">
+        <v>70</v>
+      </c>
+      <c r="C99" s="256">
+        <v>1</v>
+      </c>
+      <c r="D99" s="257"/>
+      <c r="E99" s="258"/>
+      <c r="F99" s="331">
+        <f>SUM(E99:E108)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B100" s="309"/>
+      <c r="C100" s="259">
+        <v>2</v>
+      </c>
+      <c r="D100" s="226"/>
+      <c r="E100" s="260"/>
+      <c r="F100" s="324"/>
+    </row>
+    <row r="101" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B101" s="309"/>
+      <c r="C101" s="259">
+        <v>3</v>
+      </c>
+      <c r="D101" s="226"/>
+      <c r="E101" s="260"/>
+      <c r="F101" s="324"/>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B102" s="309"/>
+      <c r="C102" s="259">
+        <v>4</v>
+      </c>
+      <c r="D102" s="226"/>
+      <c r="E102" s="260"/>
+      <c r="F102" s="324"/>
+    </row>
+    <row r="103" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B103" s="309"/>
+      <c r="C103" s="259">
+        <v>5</v>
+      </c>
+      <c r="D103" s="226"/>
+      <c r="E103" s="260"/>
+      <c r="F103" s="324"/>
+    </row>
+    <row r="104" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B104" s="309"/>
+      <c r="C104" s="259">
+        <v>6</v>
+      </c>
+      <c r="D104" s="226"/>
+      <c r="E104" s="260"/>
+      <c r="F104" s="324"/>
+    </row>
+    <row r="105" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B105" s="309"/>
+      <c r="C105" s="259">
+        <v>7</v>
+      </c>
+      <c r="D105" s="226"/>
+      <c r="E105" s="260"/>
+      <c r="F105" s="324"/>
+    </row>
+    <row r="106" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B106" s="309"/>
+      <c r="C106" s="259">
+        <v>8</v>
+      </c>
+      <c r="D106" s="226"/>
+      <c r="E106" s="260"/>
+      <c r="F106" s="324"/>
+    </row>
+    <row r="107" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B107" s="309"/>
+      <c r="C107" s="259">
+        <v>9</v>
+      </c>
+      <c r="D107" s="226"/>
+      <c r="E107" s="260"/>
+      <c r="F107" s="324"/>
+    </row>
+    <row r="108" spans="2:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B108" s="312"/>
+      <c r="C108" s="261">
+        <v>10</v>
+      </c>
+      <c r="D108" s="229"/>
+      <c r="E108" s="262"/>
+      <c r="F108" s="325"/>
+    </row>
+    <row r="109" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B109" s="311" t="s">
+        <v>71</v>
+      </c>
+      <c r="C109" s="256">
+        <v>1</v>
+      </c>
+      <c r="D109" s="257"/>
+      <c r="E109" s="258"/>
+      <c r="F109" s="323">
+        <f>SUM(E109:E118)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B110" s="309"/>
+      <c r="C110" s="259">
+        <v>2</v>
+      </c>
+      <c r="D110" s="226"/>
+      <c r="E110" s="260"/>
+      <c r="F110" s="324"/>
+    </row>
+    <row r="111" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B111" s="309"/>
+      <c r="C111" s="259">
+        <v>3</v>
+      </c>
+      <c r="D111" s="226"/>
+      <c r="E111" s="260"/>
+      <c r="F111" s="324"/>
+    </row>
+    <row r="112" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B112" s="309"/>
+      <c r="C112" s="259">
+        <v>4</v>
+      </c>
+      <c r="D112" s="226"/>
+      <c r="E112" s="260"/>
+      <c r="F112" s="324"/>
+    </row>
+    <row r="113" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B113" s="309"/>
+      <c r="C113" s="259">
+        <v>5</v>
+      </c>
+      <c r="D113" s="226"/>
+      <c r="E113" s="260"/>
+      <c r="F113" s="324"/>
+    </row>
+    <row r="114" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B114" s="309"/>
+      <c r="C114" s="259">
+        <v>6</v>
+      </c>
+      <c r="D114" s="226"/>
+      <c r="E114" s="260"/>
+      <c r="F114" s="324"/>
+    </row>
+    <row r="115" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B115" s="309"/>
+      <c r="C115" s="259">
+        <v>7</v>
+      </c>
+      <c r="D115" s="226"/>
+      <c r="E115" s="260"/>
+      <c r="F115" s="324"/>
+    </row>
+    <row r="116" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B116" s="309"/>
+      <c r="C116" s="259">
+        <v>8</v>
+      </c>
+      <c r="D116" s="226"/>
+      <c r="E116" s="260"/>
+      <c r="F116" s="324"/>
+    </row>
+    <row r="117" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B117" s="309"/>
+      <c r="C117" s="259">
+        <v>9</v>
+      </c>
+      <c r="D117" s="226"/>
+      <c r="E117" s="260"/>
+      <c r="F117" s="324"/>
+    </row>
+    <row r="118" spans="2:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B118" s="312"/>
+      <c r="C118" s="261">
+        <v>10</v>
+      </c>
+      <c r="D118" s="229"/>
+      <c r="E118" s="262"/>
+      <c r="F118" s="325"/>
+    </row>
+    <row r="119" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B119" s="311" t="s">
+        <v>72</v>
+      </c>
+      <c r="C119" s="256">
+        <v>1</v>
+      </c>
+      <c r="D119" s="257"/>
+      <c r="E119" s="258"/>
+      <c r="F119" s="323">
+        <f>SUM(E119:E128)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B120" s="309"/>
+      <c r="C120" s="259">
+        <v>2</v>
+      </c>
+      <c r="D120" s="226"/>
+      <c r="E120" s="260"/>
+      <c r="F120" s="324"/>
+    </row>
+    <row r="121" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B121" s="309"/>
+      <c r="C121" s="259">
+        <v>3</v>
+      </c>
+      <c r="D121" s="226"/>
+      <c r="E121" s="260"/>
+      <c r="F121" s="324"/>
+    </row>
+    <row r="122" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B122" s="309"/>
+      <c r="C122" s="259">
+        <v>4</v>
+      </c>
+      <c r="D122" s="226"/>
+      <c r="E122" s="260"/>
+      <c r="F122" s="324"/>
+    </row>
+    <row r="123" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B123" s="309"/>
+      <c r="C123" s="259">
+        <v>5</v>
+      </c>
+      <c r="D123" s="226"/>
+      <c r="E123" s="260"/>
+      <c r="F123" s="324"/>
+    </row>
+    <row r="124" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B124" s="309"/>
+      <c r="C124" s="259">
+        <v>6</v>
+      </c>
+      <c r="D124" s="226"/>
+      <c r="E124" s="260"/>
+      <c r="F124" s="324"/>
+    </row>
+    <row r="125" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B125" s="309"/>
+      <c r="C125" s="259">
+        <v>7</v>
+      </c>
+      <c r="D125" s="226"/>
+      <c r="E125" s="260"/>
+      <c r="F125" s="324"/>
+    </row>
+    <row r="126" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B126" s="309"/>
+      <c r="C126" s="259">
+        <v>8</v>
+      </c>
+      <c r="D126" s="226"/>
+      <c r="E126" s="260"/>
+      <c r="F126" s="324"/>
+    </row>
+    <row r="127" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B127" s="309"/>
+      <c r="C127" s="259">
+        <v>9</v>
+      </c>
+      <c r="D127" s="226"/>
+      <c r="E127" s="260"/>
+      <c r="F127" s="324"/>
+    </row>
+    <row r="128" spans="2:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B128" s="312"/>
+      <c r="C128" s="261">
+        <v>10</v>
+      </c>
+      <c r="D128" s="229"/>
+      <c r="E128" s="262"/>
+      <c r="F128" s="325"/>
+    </row>
+    <row r="129" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B129" s="313" t="s">
+        <v>73</v>
+      </c>
+      <c r="C129" s="256">
+        <v>1</v>
+      </c>
+      <c r="D129" s="257"/>
+      <c r="E129" s="258"/>
+      <c r="F129" s="323">
+        <f>SUM(E129:E131)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B130" s="309"/>
+      <c r="C130" s="259">
+        <v>2</v>
+      </c>
+      <c r="D130" s="226"/>
+      <c r="E130" s="260"/>
+      <c r="F130" s="324"/>
+    </row>
+    <row r="131" spans="2:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B131" s="309"/>
+      <c r="C131" s="259">
+        <v>3</v>
+      </c>
+      <c r="D131" s="226"/>
+      <c r="E131" s="260"/>
+      <c r="F131" s="325"/>
+    </row>
+    <row r="132" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B132" s="305" t="s">
+        <v>74</v>
+      </c>
+      <c r="C132" s="263">
+        <v>1</v>
+      </c>
+      <c r="D132" s="264"/>
+      <c r="E132" s="265"/>
+      <c r="F132" s="321">
+        <f>SUM(E132:E140)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B133" s="306"/>
+      <c r="C133" s="266">
+        <v>2</v>
+      </c>
+      <c r="D133" s="267"/>
+      <c r="E133" s="268"/>
+      <c r="F133" s="304"/>
+    </row>
+    <row r="134" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B134" s="306"/>
+      <c r="C134" s="266">
+        <v>3</v>
+      </c>
+      <c r="D134" s="267"/>
+      <c r="E134" s="268"/>
+      <c r="F134" s="304"/>
+    </row>
+    <row r="135" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B135" s="306"/>
+      <c r="C135" s="266">
+        <v>4</v>
+      </c>
+      <c r="D135" s="267"/>
+      <c r="E135" s="268"/>
+      <c r="F135" s="304"/>
+    </row>
+    <row r="136" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B136" s="306"/>
+      <c r="C136" s="266">
+        <v>5</v>
+      </c>
+      <c r="D136" s="267"/>
+      <c r="E136" s="268"/>
+      <c r="F136" s="304"/>
+    </row>
+    <row r="137" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B137" s="306"/>
+      <c r="C137" s="266">
+        <v>6</v>
+      </c>
+      <c r="D137" s="267"/>
+      <c r="E137" s="268"/>
+      <c r="F137" s="304"/>
+    </row>
+    <row r="138" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B138" s="306"/>
+      <c r="C138" s="266">
+        <v>7</v>
+      </c>
+      <c r="D138" s="267"/>
+      <c r="E138" s="268"/>
+      <c r="F138" s="304"/>
+    </row>
+    <row r="139" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B139" s="306"/>
+      <c r="C139" s="269">
+        <v>8</v>
+      </c>
+      <c r="D139" s="270"/>
+      <c r="E139" s="271"/>
+      <c r="F139" s="304"/>
+    </row>
+    <row r="140" spans="2:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B140" s="307"/>
+      <c r="C140" s="272">
+        <v>9</v>
+      </c>
+      <c r="D140" s="273"/>
+      <c r="E140" s="274"/>
+      <c r="F140" s="322"/>
+    </row>
+    <row r="141" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B141" s="311" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B99" s="307" t="s">
-        <v>71</v>
-      </c>
-      <c r="C99" s="258">
+      <c r="C141" s="275">
         <v>1</v>
       </c>
-      <c r="D99" s="259"/>
-      <c r="E99" s="260"/>
-      <c r="F99" s="324">
-        <f>SUM(E99:E108)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B100" s="308"/>
-      <c r="C100" s="261">
+      <c r="D141" s="276"/>
+      <c r="E141" s="277"/>
+      <c r="F141" s="323">
+        <f>SUM(E141:E150)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B142" s="309"/>
+      <c r="C142" s="259">
         <v>2</v>
       </c>
-      <c r="D100" s="226"/>
-      <c r="E100" s="262"/>
-      <c r="F100" s="301"/>
-    </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B101" s="308"/>
-      <c r="C101" s="261">
+      <c r="D142" s="226"/>
+      <c r="E142" s="260"/>
+      <c r="F142" s="324"/>
+    </row>
+    <row r="143" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B143" s="309"/>
+      <c r="C143" s="259">
         <v>3</v>
       </c>
-      <c r="D101" s="226"/>
-      <c r="E101" s="262"/>
-      <c r="F101" s="301"/>
-    </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B102" s="308"/>
-      <c r="C102" s="261">
+      <c r="D143" s="226"/>
+      <c r="E143" s="260"/>
+      <c r="F143" s="324"/>
+    </row>
+    <row r="144" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B144" s="309"/>
+      <c r="C144" s="259">
         <v>4</v>
       </c>
-      <c r="D102" s="226"/>
-      <c r="E102" s="262"/>
-      <c r="F102" s="301"/>
-    </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B103" s="308"/>
-      <c r="C103" s="261">
+      <c r="D144" s="226"/>
+      <c r="E144" s="260"/>
+      <c r="F144" s="324"/>
+    </row>
+    <row r="145" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B145" s="309"/>
+      <c r="C145" s="259">
         <v>5</v>
       </c>
-      <c r="D103" s="226"/>
-      <c r="E103" s="262"/>
-      <c r="F103" s="301"/>
-    </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B104" s="308"/>
-      <c r="C104" s="261">
+      <c r="D145" s="226"/>
+      <c r="E145" s="260"/>
+      <c r="F145" s="324"/>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B146" s="309"/>
+      <c r="C146" s="259">
         <v>6</v>
       </c>
-      <c r="D104" s="226"/>
-      <c r="E104" s="262"/>
-      <c r="F104" s="301"/>
-    </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B105" s="308"/>
-      <c r="C105" s="261">
+      <c r="D146" s="226"/>
+      <c r="E146" s="260"/>
+      <c r="F146" s="324"/>
+    </row>
+    <row r="147" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B147" s="309"/>
+      <c r="C147" s="259">
         <v>7</v>
       </c>
-      <c r="D105" s="226"/>
-      <c r="E105" s="262"/>
-      <c r="F105" s="301"/>
-    </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B106" s="308"/>
-      <c r="C106" s="261">
+      <c r="D147" s="226"/>
+      <c r="E147" s="260"/>
+      <c r="F147" s="324"/>
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B148" s="309"/>
+      <c r="C148" s="259">
         <v>8</v>
       </c>
-      <c r="D106" s="226"/>
-      <c r="E106" s="262"/>
-      <c r="F106" s="301"/>
-    </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B107" s="308"/>
-      <c r="C107" s="261">
+      <c r="D148" s="226"/>
+      <c r="E148" s="260"/>
+      <c r="F148" s="324"/>
+    </row>
+    <row r="149" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B149" s="309"/>
+      <c r="C149" s="259">
         <v>9</v>
       </c>
-      <c r="D107" s="226"/>
-      <c r="E107" s="262"/>
-      <c r="F107" s="301"/>
-    </row>
-    <row r="108" spans="2:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B108" s="309"/>
-      <c r="C108" s="263">
+      <c r="D149" s="226"/>
+      <c r="E149" s="260"/>
+      <c r="F149" s="324"/>
+    </row>
+    <row r="150" spans="2:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B150" s="312"/>
+      <c r="C150" s="278">
         <v>10</v>
       </c>
-      <c r="D108" s="229"/>
-      <c r="E108" s="264"/>
-      <c r="F108" s="302"/>
-    </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B109" s="307" t="s">
-        <v>72</v>
-      </c>
-      <c r="C109" s="258">
+      <c r="D150" s="279"/>
+      <c r="E150" s="280"/>
+      <c r="F150" s="325"/>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B151" s="311" t="s">
+        <v>118</v>
+      </c>
+      <c r="C151" s="281">
         <v>1</v>
       </c>
-      <c r="D109" s="259"/>
-      <c r="E109" s="260"/>
-      <c r="F109" s="300">
-        <f>SUM(E109:E118)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B110" s="308"/>
-      <c r="C110" s="261">
+      <c r="D151" s="257"/>
+      <c r="E151" s="282"/>
+      <c r="F151" s="328">
+        <f>SUM(E151:E160)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B152" s="309"/>
+      <c r="C152" s="283">
         <v>2</v>
       </c>
-      <c r="D110" s="226"/>
-      <c r="E110" s="262"/>
-      <c r="F110" s="301"/>
-    </row>
-    <row r="111" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B111" s="308"/>
-      <c r="C111" s="261">
+      <c r="D152" s="226"/>
+      <c r="E152" s="284"/>
+      <c r="F152" s="309"/>
+    </row>
+    <row r="153" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B153" s="309"/>
+      <c r="C153" s="283">
         <v>3</v>
       </c>
-      <c r="D111" s="226"/>
-      <c r="E111" s="262"/>
-      <c r="F111" s="301"/>
-    </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B112" s="308"/>
-      <c r="C112" s="261">
+      <c r="D153" s="226"/>
+      <c r="E153" s="284"/>
+      <c r="F153" s="309"/>
+    </row>
+    <row r="154" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B154" s="309"/>
+      <c r="C154" s="283">
         <v>4</v>
       </c>
-      <c r="D112" s="226"/>
-      <c r="E112" s="262"/>
-      <c r="F112" s="301"/>
-    </row>
-    <row r="113" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B113" s="308"/>
-      <c r="C113" s="261">
+      <c r="D154" s="226"/>
+      <c r="E154" s="284"/>
+      <c r="F154" s="309"/>
+    </row>
+    <row r="155" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B155" s="309"/>
+      <c r="C155" s="283">
         <v>5</v>
       </c>
-      <c r="D113" s="226"/>
-      <c r="E113" s="262"/>
-      <c r="F113" s="301"/>
-    </row>
-    <row r="114" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B114" s="308"/>
-      <c r="C114" s="261">
+      <c r="D155" s="226"/>
+      <c r="E155" s="284"/>
+      <c r="F155" s="309"/>
+    </row>
+    <row r="156" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B156" s="309"/>
+      <c r="C156" s="283">
         <v>6</v>
       </c>
-      <c r="D114" s="226"/>
-      <c r="E114" s="262"/>
-      <c r="F114" s="301"/>
-    </row>
-    <row r="115" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B115" s="308"/>
-      <c r="C115" s="261">
+      <c r="D156" s="226"/>
+      <c r="E156" s="284"/>
+      <c r="F156" s="309"/>
+    </row>
+    <row r="157" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B157" s="309"/>
+      <c r="C157" s="283">
         <v>7</v>
       </c>
-      <c r="D115" s="226"/>
-      <c r="E115" s="262"/>
-      <c r="F115" s="301"/>
-    </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B116" s="308"/>
-      <c r="C116" s="261">
+      <c r="D157" s="226"/>
+      <c r="E157" s="284"/>
+      <c r="F157" s="309"/>
+    </row>
+    <row r="158" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B158" s="309"/>
+      <c r="C158" s="283">
         <v>8</v>
       </c>
-      <c r="D116" s="226"/>
-      <c r="E116" s="262"/>
-      <c r="F116" s="301"/>
-    </row>
-    <row r="117" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B117" s="308"/>
-      <c r="C117" s="261">
+      <c r="D158" s="226"/>
+      <c r="E158" s="284"/>
+      <c r="F158" s="309"/>
+    </row>
+    <row r="159" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B159" s="309"/>
+      <c r="C159" s="283">
         <v>9</v>
       </c>
-      <c r="D117" s="226"/>
-      <c r="E117" s="262"/>
-      <c r="F117" s="301"/>
-    </row>
-    <row r="118" spans="2:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B118" s="309"/>
-      <c r="C118" s="263">
+      <c r="D159" s="226"/>
+      <c r="E159" s="284"/>
+      <c r="F159" s="309"/>
+    </row>
+    <row r="160" spans="2:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B160" s="312"/>
+      <c r="C160" s="285">
         <v>10</v>
       </c>
-      <c r="D118" s="229"/>
-      <c r="E118" s="264"/>
-      <c r="F118" s="302"/>
-    </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B119" s="307" t="s">
-        <v>73</v>
-      </c>
-      <c r="C119" s="258">
+      <c r="D160" s="229"/>
+      <c r="E160" s="286"/>
+      <c r="F160" s="312"/>
+    </row>
+    <row r="161" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B161" s="320" t="s">
+        <v>76</v>
+      </c>
+      <c r="C161" s="281">
         <v>1</v>
       </c>
-      <c r="D119" s="259"/>
-      <c r="E119" s="260"/>
-      <c r="F119" s="300">
-        <f>SUM(E119:E128)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B120" s="308"/>
-      <c r="C120" s="261">
+      <c r="D161" s="257"/>
+      <c r="E161" s="258"/>
+      <c r="F161" s="326">
+        <f>SUM(E161:E170)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B162" s="309"/>
+      <c r="C162" s="283">
         <v>2</v>
       </c>
-      <c r="D120" s="226"/>
-      <c r="E120" s="262"/>
-      <c r="F120" s="301"/>
-    </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B121" s="308"/>
-      <c r="C121" s="261">
+      <c r="D162" s="226"/>
+      <c r="E162" s="260"/>
+      <c r="F162" s="324"/>
+    </row>
+    <row r="163" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B163" s="309"/>
+      <c r="C163" s="283">
         <v>3</v>
       </c>
-      <c r="D121" s="226"/>
-      <c r="E121" s="262"/>
-      <c r="F121" s="301"/>
-    </row>
-    <row r="122" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="308"/>
-      <c r="C122" s="261">
+      <c r="D163" s="226"/>
+      <c r="E163" s="260"/>
+      <c r="F163" s="324"/>
+    </row>
+    <row r="164" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B164" s="309"/>
+      <c r="C164" s="283">
         <v>4</v>
       </c>
-      <c r="D122" s="226"/>
-      <c r="E122" s="262"/>
-      <c r="F122" s="301"/>
-    </row>
-    <row r="123" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="308"/>
-      <c r="C123" s="261">
+      <c r="D164" s="226"/>
+      <c r="E164" s="260"/>
+      <c r="F164" s="324"/>
+    </row>
+    <row r="165" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B165" s="309"/>
+      <c r="C165" s="283">
         <v>5</v>
       </c>
-      <c r="D123" s="226"/>
-      <c r="E123" s="262"/>
-      <c r="F123" s="301"/>
-    </row>
-    <row r="124" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="308"/>
-      <c r="C124" s="261">
+      <c r="D165" s="226"/>
+      <c r="E165" s="260"/>
+      <c r="F165" s="324"/>
+    </row>
+    <row r="166" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B166" s="309"/>
+      <c r="C166" s="283">
         <v>6</v>
       </c>
-      <c r="D124" s="226"/>
-      <c r="E124" s="262"/>
-      <c r="F124" s="301"/>
-    </row>
-    <row r="125" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="308"/>
-      <c r="C125" s="261">
+      <c r="D166" s="226"/>
+      <c r="E166" s="260"/>
+      <c r="F166" s="324"/>
+    </row>
+    <row r="167" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B167" s="309"/>
+      <c r="C167" s="283">
         <v>7</v>
       </c>
-      <c r="D125" s="226"/>
-      <c r="E125" s="262"/>
-      <c r="F125" s="301"/>
-    </row>
-    <row r="126" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="308"/>
-      <c r="C126" s="261">
+      <c r="D167" s="226"/>
+      <c r="E167" s="260"/>
+      <c r="F167" s="324"/>
+    </row>
+    <row r="168" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B168" s="309"/>
+      <c r="C168" s="283">
         <v>8</v>
       </c>
-      <c r="D126" s="226"/>
-      <c r="E126" s="262"/>
-      <c r="F126" s="301"/>
-    </row>
-    <row r="127" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B127" s="308"/>
-      <c r="C127" s="261">
+      <c r="D168" s="226"/>
+      <c r="E168" s="260"/>
+      <c r="F168" s="324"/>
+    </row>
+    <row r="169" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B169" s="309"/>
+      <c r="C169" s="283">
         <v>9</v>
       </c>
-      <c r="D127" s="226"/>
-      <c r="E127" s="262"/>
-      <c r="F127" s="301"/>
-    </row>
-    <row r="128" spans="2:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B128" s="309"/>
-      <c r="C128" s="263">
+      <c r="D169" s="226"/>
+      <c r="E169" s="260"/>
+      <c r="F169" s="324"/>
+    </row>
+    <row r="170" spans="2:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B170" s="312"/>
+      <c r="C170" s="285">
         <v>10</v>
       </c>
-      <c r="D128" s="229"/>
-      <c r="E128" s="264"/>
-      <c r="F128" s="302"/>
-    </row>
-    <row r="129" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B129" s="314" t="s">
-        <v>74</v>
-      </c>
-      <c r="C129" s="258">
+      <c r="D170" s="229"/>
+      <c r="E170" s="262"/>
+      <c r="F170" s="327"/>
+    </row>
+    <row r="171" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B171" s="313" t="s">
+        <v>77</v>
+      </c>
+      <c r="C171" s="275">
         <v>1</v>
       </c>
-      <c r="D129" s="259"/>
-      <c r="E129" s="260"/>
-      <c r="F129" s="300">
-        <f>SUM(E129:E131)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B130" s="308"/>
-      <c r="C130" s="261">
+      <c r="D171" s="276"/>
+      <c r="E171" s="277"/>
+      <c r="F171" s="326">
+        <f>SUM(E171:E179)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B172" s="309"/>
+      <c r="C172" s="259">
         <v>2</v>
       </c>
-      <c r="D130" s="226"/>
-      <c r="E130" s="262"/>
-      <c r="F130" s="301"/>
-    </row>
-    <row r="131" spans="2:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B131" s="308"/>
-      <c r="C131" s="261">
+      <c r="D172" s="226"/>
+      <c r="E172" s="260"/>
+      <c r="F172" s="324"/>
+    </row>
+    <row r="173" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B173" s="309"/>
+      <c r="C173" s="259">
         <v>3</v>
       </c>
-      <c r="D131" s="226"/>
-      <c r="E131" s="262"/>
-      <c r="F131" s="302"/>
-    </row>
-    <row r="132" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B132" s="330" t="s">
-        <v>75</v>
-      </c>
-      <c r="C132" s="265">
+      <c r="D173" s="226"/>
+      <c r="E173" s="260"/>
+      <c r="F173" s="324"/>
+    </row>
+    <row r="174" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B174" s="309"/>
+      <c r="C174" s="259">
+        <v>4</v>
+      </c>
+      <c r="D174" s="226"/>
+      <c r="E174" s="260"/>
+      <c r="F174" s="324"/>
+    </row>
+    <row r="175" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B175" s="309"/>
+      <c r="C175" s="259">
+        <v>5</v>
+      </c>
+      <c r="D175" s="226"/>
+      <c r="E175" s="260"/>
+      <c r="F175" s="324"/>
+    </row>
+    <row r="176" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B176" s="309"/>
+      <c r="C176" s="259">
+        <v>6</v>
+      </c>
+      <c r="D176" s="226"/>
+      <c r="E176" s="260"/>
+      <c r="F176" s="324"/>
+    </row>
+    <row r="177" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B177" s="309"/>
+      <c r="C177" s="259">
+        <v>7</v>
+      </c>
+      <c r="D177" s="226"/>
+      <c r="E177" s="260"/>
+      <c r="F177" s="324"/>
+    </row>
+    <row r="178" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B178" s="309"/>
+      <c r="C178" s="259">
+        <v>8</v>
+      </c>
+      <c r="D178" s="226"/>
+      <c r="E178" s="260"/>
+      <c r="F178" s="324"/>
+    </row>
+    <row r="179" spans="2:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B179" s="309"/>
+      <c r="C179" s="278">
+        <v>9</v>
+      </c>
+      <c r="D179" s="279"/>
+      <c r="E179" s="280"/>
+      <c r="F179" s="327"/>
+    </row>
+    <row r="180" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B180" s="305" t="s">
+        <v>78</v>
+      </c>
+      <c r="C180" s="263">
         <v>1</v>
       </c>
-      <c r="D132" s="266"/>
-      <c r="E132" s="267"/>
-      <c r="F132" s="318">
-        <f>SUM(E132:E140)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B133" s="331"/>
-      <c r="C133" s="268">
+      <c r="D180" s="264"/>
+      <c r="E180" s="287"/>
+      <c r="F180" s="326">
+        <f>SUM(E180:E189)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B181" s="306"/>
+      <c r="C181" s="269">
         <v>2</v>
       </c>
-      <c r="D133" s="269"/>
-      <c r="E133" s="270"/>
-      <c r="F133" s="319"/>
-    </row>
-    <row r="134" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B134" s="331"/>
-      <c r="C134" s="268">
+      <c r="D181" s="270"/>
+      <c r="E181" s="288"/>
+      <c r="F181" s="324"/>
+    </row>
+    <row r="182" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B182" s="306"/>
+      <c r="C182" s="269">
         <v>3</v>
       </c>
-      <c r="D134" s="269"/>
-      <c r="E134" s="270"/>
-      <c r="F134" s="319"/>
-    </row>
-    <row r="135" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B135" s="331"/>
-      <c r="C135" s="268">
+      <c r="D182" s="270"/>
+      <c r="E182" s="288"/>
+      <c r="F182" s="324"/>
+    </row>
+    <row r="183" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B183" s="306"/>
+      <c r="C183" s="269">
         <v>4</v>
       </c>
-      <c r="D135" s="269"/>
-      <c r="E135" s="270"/>
-      <c r="F135" s="319"/>
-    </row>
-    <row r="136" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B136" s="331"/>
-      <c r="C136" s="268">
+      <c r="D183" s="270"/>
+      <c r="E183" s="288"/>
+      <c r="F183" s="324"/>
+    </row>
+    <row r="184" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B184" s="306"/>
+      <c r="C184" s="269">
         <v>5</v>
       </c>
-      <c r="D136" s="269"/>
-      <c r="E136" s="270"/>
-      <c r="F136" s="319"/>
-    </row>
-    <row r="137" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B137" s="331"/>
-      <c r="C137" s="268">
+      <c r="D184" s="270"/>
+      <c r="E184" s="288"/>
+      <c r="F184" s="324"/>
+    </row>
+    <row r="185" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B185" s="306"/>
+      <c r="C185" s="269">
         <v>6</v>
       </c>
-      <c r="D137" s="269"/>
-      <c r="E137" s="270"/>
-      <c r="F137" s="319"/>
-    </row>
-    <row r="138" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B138" s="331"/>
-      <c r="C138" s="268">
+      <c r="D185" s="270"/>
+      <c r="E185" s="288"/>
+      <c r="F185" s="324"/>
+    </row>
+    <row r="186" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B186" s="306"/>
+      <c r="C186" s="269">
         <v>7</v>
       </c>
-      <c r="D138" s="269"/>
-      <c r="E138" s="270"/>
-      <c r="F138" s="319"/>
-    </row>
-    <row r="139" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B139" s="331"/>
-      <c r="C139" s="271">
+      <c r="D186" s="270"/>
+      <c r="E186" s="288"/>
+      <c r="F186" s="324"/>
+    </row>
+    <row r="187" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B187" s="306"/>
+      <c r="C187" s="269">
         <v>8</v>
       </c>
-      <c r="D139" s="272"/>
-      <c r="E139" s="273"/>
-      <c r="F139" s="319"/>
-    </row>
-    <row r="140" spans="2:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B140" s="332"/>
-      <c r="C140" s="274">
+      <c r="D187" s="270"/>
+      <c r="E187" s="288"/>
+      <c r="F187" s="324"/>
+    </row>
+    <row r="188" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B188" s="306"/>
+      <c r="C188" s="269">
         <v>9</v>
       </c>
-      <c r="D140" s="275"/>
-      <c r="E140" s="276"/>
-      <c r="F140" s="320"/>
-    </row>
-    <row r="141" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B141" s="307" t="s">
-        <v>118</v>
-      </c>
-      <c r="C141" s="277">
+      <c r="D188" s="270"/>
+      <c r="E188" s="288"/>
+      <c r="F188" s="324"/>
+    </row>
+    <row r="189" spans="2:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B189" s="307"/>
+      <c r="C189" s="272">
+        <v>10</v>
+      </c>
+      <c r="D189" s="273"/>
+      <c r="E189" s="289"/>
+      <c r="F189" s="327"/>
+    </row>
+    <row r="190" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B190" s="305" t="s">
+        <v>79</v>
+      </c>
+      <c r="C190" s="263">
         <v>1</v>
       </c>
-      <c r="D141" s="278"/>
-      <c r="E141" s="279"/>
-      <c r="F141" s="300">
-        <f>SUM(E141:E150)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B142" s="308"/>
-      <c r="C142" s="261">
+      <c r="D190" s="264"/>
+      <c r="E190" s="287"/>
+      <c r="F190" s="326">
+        <f>SUM(E190:E199)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B191" s="306"/>
+      <c r="C191" s="269">
         <v>2</v>
       </c>
-      <c r="D142" s="226"/>
-      <c r="E142" s="262"/>
-      <c r="F142" s="301"/>
-    </row>
-    <row r="143" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B143" s="308"/>
-      <c r="C143" s="261">
+      <c r="D191" s="270"/>
+      <c r="E191" s="288"/>
+      <c r="F191" s="324"/>
+    </row>
+    <row r="192" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B192" s="306"/>
+      <c r="C192" s="269">
         <v>3</v>
       </c>
-      <c r="D143" s="226"/>
-      <c r="E143" s="262"/>
-      <c r="F143" s="301"/>
-    </row>
-    <row r="144" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B144" s="308"/>
-      <c r="C144" s="261">
+      <c r="D192" s="270"/>
+      <c r="E192" s="288"/>
+      <c r="F192" s="324"/>
+    </row>
+    <row r="193" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B193" s="306"/>
+      <c r="C193" s="269">
         <v>4</v>
       </c>
-      <c r="D144" s="226"/>
-      <c r="E144" s="262"/>
-      <c r="F144" s="301"/>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B145" s="308"/>
-      <c r="C145" s="261">
+      <c r="D193" s="270"/>
+      <c r="E193" s="288"/>
+      <c r="F193" s="324"/>
+    </row>
+    <row r="194" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B194" s="306"/>
+      <c r="C194" s="269">
         <v>5</v>
       </c>
-      <c r="D145" s="226"/>
-      <c r="E145" s="262"/>
-      <c r="F145" s="301"/>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B146" s="308"/>
-      <c r="C146" s="261">
+      <c r="D194" s="270"/>
+      <c r="E194" s="288"/>
+      <c r="F194" s="324"/>
+    </row>
+    <row r="195" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B195" s="306"/>
+      <c r="C195" s="269">
         <v>6</v>
       </c>
-      <c r="D146" s="226"/>
-      <c r="E146" s="262"/>
-      <c r="F146" s="301"/>
-    </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B147" s="308"/>
-      <c r="C147" s="261">
+      <c r="D195" s="270"/>
+      <c r="E195" s="288"/>
+      <c r="F195" s="324"/>
+    </row>
+    <row r="196" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B196" s="306"/>
+      <c r="C196" s="269">
         <v>7</v>
       </c>
-      <c r="D147" s="226"/>
-      <c r="E147" s="262"/>
-      <c r="F147" s="301"/>
-    </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B148" s="308"/>
-      <c r="C148" s="261">
+      <c r="D196" s="270"/>
+      <c r="E196" s="288"/>
+      <c r="F196" s="324"/>
+    </row>
+    <row r="197" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B197" s="306"/>
+      <c r="C197" s="269">
         <v>8</v>
       </c>
-      <c r="D148" s="226"/>
-      <c r="E148" s="262"/>
-      <c r="F148" s="301"/>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B149" s="308"/>
-      <c r="C149" s="261">
+      <c r="D197" s="270"/>
+      <c r="E197" s="288"/>
+      <c r="F197" s="324"/>
+    </row>
+    <row r="198" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B198" s="306"/>
+      <c r="C198" s="269">
         <v>9</v>
       </c>
-      <c r="D149" s="226"/>
-      <c r="E149" s="262"/>
-      <c r="F149" s="301"/>
-    </row>
-    <row r="150" spans="2:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B150" s="309"/>
-      <c r="C150" s="280">
+      <c r="D198" s="270"/>
+      <c r="E198" s="288"/>
+      <c r="F198" s="324"/>
+    </row>
+    <row r="199" spans="2:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B199" s="307"/>
+      <c r="C199" s="272">
         <v>10</v>
       </c>
-      <c r="D150" s="281"/>
-      <c r="E150" s="282"/>
-      <c r="F150" s="302"/>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B151" s="307" t="s">
-        <v>119</v>
-      </c>
-      <c r="C151" s="283">
-        <v>1</v>
-      </c>
-      <c r="D151" s="259"/>
-      <c r="E151" s="284"/>
-      <c r="F151" s="321">
-        <f>SUM(E151:E160)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B152" s="308"/>
-      <c r="C152" s="285">
-        <v>2</v>
-      </c>
-      <c r="D152" s="226"/>
-      <c r="E152" s="286"/>
-      <c r="F152" s="308"/>
-    </row>
-    <row r="153" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B153" s="308"/>
-      <c r="C153" s="285">
-        <v>3</v>
-      </c>
-      <c r="D153" s="226"/>
-      <c r="E153" s="286"/>
-      <c r="F153" s="308"/>
-    </row>
-    <row r="154" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B154" s="308"/>
-      <c r="C154" s="285">
-        <v>4</v>
-      </c>
-      <c r="D154" s="226"/>
-      <c r="E154" s="286"/>
-      <c r="F154" s="308"/>
-    </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B155" s="308"/>
-      <c r="C155" s="285">
-        <v>5</v>
-      </c>
-      <c r="D155" s="226"/>
-      <c r="E155" s="286"/>
-      <c r="F155" s="308"/>
-    </row>
-    <row r="156" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B156" s="308"/>
-      <c r="C156" s="285">
-        <v>6</v>
-      </c>
-      <c r="D156" s="226"/>
-      <c r="E156" s="286"/>
-      <c r="F156" s="308"/>
-    </row>
-    <row r="157" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B157" s="308"/>
-      <c r="C157" s="285">
-        <v>7</v>
-      </c>
-      <c r="D157" s="226"/>
-      <c r="E157" s="286"/>
-      <c r="F157" s="308"/>
-    </row>
-    <row r="158" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B158" s="308"/>
-      <c r="C158" s="285">
-        <v>8</v>
-      </c>
-      <c r="D158" s="226"/>
-      <c r="E158" s="286"/>
-      <c r="F158" s="308"/>
-    </row>
-    <row r="159" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B159" s="308"/>
-      <c r="C159" s="285">
-        <v>9</v>
-      </c>
-      <c r="D159" s="226"/>
-      <c r="E159" s="286"/>
-      <c r="F159" s="308"/>
-    </row>
-    <row r="160" spans="2:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B160" s="309"/>
-      <c r="C160" s="287">
-        <v>10</v>
-      </c>
-      <c r="D160" s="229"/>
-      <c r="E160" s="288"/>
-      <c r="F160" s="309"/>
-    </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B161" s="317" t="s">
-        <v>77</v>
-      </c>
-      <c r="C161" s="283">
-        <v>1</v>
-      </c>
-      <c r="D161" s="259"/>
-      <c r="E161" s="260"/>
-      <c r="F161" s="305">
-        <f>SUM(E161:E170)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B162" s="308"/>
-      <c r="C162" s="285">
-        <v>2</v>
-      </c>
-      <c r="D162" s="226"/>
-      <c r="E162" s="262"/>
-      <c r="F162" s="301"/>
-    </row>
-    <row r="163" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B163" s="308"/>
-      <c r="C163" s="285">
-        <v>3</v>
-      </c>
-      <c r="D163" s="226"/>
-      <c r="E163" s="262"/>
-      <c r="F163" s="301"/>
-    </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B164" s="308"/>
-      <c r="C164" s="285">
-        <v>4</v>
-      </c>
-      <c r="D164" s="226"/>
-      <c r="E164" s="262"/>
-      <c r="F164" s="301"/>
-    </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B165" s="308"/>
-      <c r="C165" s="285">
-        <v>5</v>
-      </c>
-      <c r="D165" s="226"/>
-      <c r="E165" s="262"/>
-      <c r="F165" s="301"/>
-    </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B166" s="308"/>
-      <c r="C166" s="285">
-        <v>6</v>
-      </c>
-      <c r="D166" s="226"/>
-      <c r="E166" s="262"/>
-      <c r="F166" s="301"/>
-    </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B167" s="308"/>
-      <c r="C167" s="285">
-        <v>7</v>
-      </c>
-      <c r="D167" s="226"/>
-      <c r="E167" s="262"/>
-      <c r="F167" s="301"/>
-    </row>
-    <row r="168" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B168" s="308"/>
-      <c r="C168" s="285">
-        <v>8</v>
-      </c>
-      <c r="D168" s="226"/>
-      <c r="E168" s="262"/>
-      <c r="F168" s="301"/>
-    </row>
-    <row r="169" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B169" s="308"/>
-      <c r="C169" s="285">
-        <v>9</v>
-      </c>
-      <c r="D169" s="226"/>
-      <c r="E169" s="262"/>
-      <c r="F169" s="301"/>
-    </row>
-    <row r="170" spans="2:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B170" s="309"/>
-      <c r="C170" s="287">
-        <v>10</v>
-      </c>
-      <c r="D170" s="229"/>
-      <c r="E170" s="264"/>
-      <c r="F170" s="306"/>
-    </row>
-    <row r="171" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B171" s="314" t="s">
-        <v>78</v>
-      </c>
-      <c r="C171" s="277">
-        <v>1</v>
-      </c>
-      <c r="D171" s="278"/>
-      <c r="E171" s="279"/>
-      <c r="F171" s="305">
-        <f>SUM(E171:E179)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B172" s="308"/>
-      <c r="C172" s="261">
-        <v>2</v>
-      </c>
-      <c r="D172" s="226"/>
-      <c r="E172" s="262"/>
-      <c r="F172" s="301"/>
-    </row>
-    <row r="173" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B173" s="308"/>
-      <c r="C173" s="261">
-        <v>3</v>
-      </c>
-      <c r="D173" s="226"/>
-      <c r="E173" s="262"/>
-      <c r="F173" s="301"/>
-    </row>
-    <row r="174" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B174" s="308"/>
-      <c r="C174" s="261">
-        <v>4</v>
-      </c>
-      <c r="D174" s="226"/>
-      <c r="E174" s="262"/>
-      <c r="F174" s="301"/>
-    </row>
-    <row r="175" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B175" s="308"/>
-      <c r="C175" s="261">
-        <v>5</v>
-      </c>
-      <c r="D175" s="226"/>
-      <c r="E175" s="262"/>
-      <c r="F175" s="301"/>
-    </row>
-    <row r="176" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B176" s="308"/>
-      <c r="C176" s="261">
-        <v>6</v>
-      </c>
-      <c r="D176" s="226"/>
-      <c r="E176" s="262"/>
-      <c r="F176" s="301"/>
-    </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B177" s="308"/>
-      <c r="C177" s="261">
-        <v>7</v>
-      </c>
-      <c r="D177" s="226"/>
-      <c r="E177" s="262"/>
-      <c r="F177" s="301"/>
-    </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B178" s="308"/>
-      <c r="C178" s="261">
-        <v>8</v>
-      </c>
-      <c r="D178" s="226"/>
-      <c r="E178" s="262"/>
-      <c r="F178" s="301"/>
-    </row>
-    <row r="179" spans="2:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B179" s="308"/>
-      <c r="C179" s="280">
-        <v>9</v>
-      </c>
-      <c r="D179" s="281"/>
-      <c r="E179" s="282"/>
-      <c r="F179" s="306"/>
-    </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B180" s="330" t="s">
-        <v>79</v>
-      </c>
-      <c r="C180" s="265">
-        <v>1</v>
-      </c>
-      <c r="D180" s="266"/>
-      <c r="E180" s="289"/>
-      <c r="F180" s="305">
-        <f>SUM(E180:E189)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B181" s="331"/>
-      <c r="C181" s="271">
-        <v>2</v>
-      </c>
-      <c r="D181" s="272"/>
-      <c r="E181" s="290"/>
-      <c r="F181" s="301"/>
-    </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B182" s="331"/>
-      <c r="C182" s="271">
-        <v>3</v>
-      </c>
-      <c r="D182" s="272"/>
-      <c r="E182" s="290"/>
-      <c r="F182" s="301"/>
-    </row>
-    <row r="183" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B183" s="331"/>
-      <c r="C183" s="271">
-        <v>4</v>
-      </c>
-      <c r="D183" s="272"/>
-      <c r="E183" s="290"/>
-      <c r="F183" s="301"/>
-    </row>
-    <row r="184" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B184" s="331"/>
-      <c r="C184" s="271">
-        <v>5</v>
-      </c>
-      <c r="D184" s="272"/>
-      <c r="E184" s="290"/>
-      <c r="F184" s="301"/>
-    </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B185" s="331"/>
-      <c r="C185" s="271">
-        <v>6</v>
-      </c>
-      <c r="D185" s="272"/>
-      <c r="E185" s="290"/>
-      <c r="F185" s="301"/>
-    </row>
-    <row r="186" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B186" s="331"/>
-      <c r="C186" s="271">
-        <v>7</v>
-      </c>
-      <c r="D186" s="272"/>
-      <c r="E186" s="290"/>
-      <c r="F186" s="301"/>
-    </row>
-    <row r="187" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B187" s="331"/>
-      <c r="C187" s="271">
-        <v>8</v>
-      </c>
-      <c r="D187" s="272"/>
-      <c r="E187" s="290"/>
-      <c r="F187" s="301"/>
-    </row>
-    <row r="188" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B188" s="331"/>
-      <c r="C188" s="271">
-        <v>9</v>
-      </c>
-      <c r="D188" s="272"/>
-      <c r="E188" s="290"/>
-      <c r="F188" s="301"/>
-    </row>
-    <row r="189" spans="2:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B189" s="332"/>
-      <c r="C189" s="274">
-        <v>10</v>
-      </c>
-      <c r="D189" s="275"/>
-      <c r="E189" s="291"/>
-      <c r="F189" s="306"/>
-    </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B190" s="330" t="s">
-        <v>80</v>
-      </c>
-      <c r="C190" s="265">
-        <v>1</v>
-      </c>
-      <c r="D190" s="266"/>
-      <c r="E190" s="289"/>
-      <c r="F190" s="305">
-        <f>SUM(E190:E199)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B191" s="331"/>
-      <c r="C191" s="271">
-        <v>2</v>
-      </c>
-      <c r="D191" s="272"/>
-      <c r="E191" s="290"/>
-      <c r="F191" s="301"/>
-    </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B192" s="331"/>
-      <c r="C192" s="271">
-        <v>3</v>
-      </c>
-      <c r="D192" s="272"/>
-      <c r="E192" s="290"/>
-      <c r="F192" s="301"/>
-    </row>
-    <row r="193" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B193" s="331"/>
-      <c r="C193" s="271">
-        <v>4</v>
-      </c>
-      <c r="D193" s="272"/>
-      <c r="E193" s="290"/>
-      <c r="F193" s="301"/>
-    </row>
-    <row r="194" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B194" s="331"/>
-      <c r="C194" s="271">
-        <v>5</v>
-      </c>
-      <c r="D194" s="272"/>
-      <c r="E194" s="290"/>
-      <c r="F194" s="301"/>
-    </row>
-    <row r="195" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B195" s="331"/>
-      <c r="C195" s="271">
-        <v>6</v>
-      </c>
-      <c r="D195" s="272"/>
-      <c r="E195" s="290"/>
-      <c r="F195" s="301"/>
-    </row>
-    <row r="196" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B196" s="331"/>
-      <c r="C196" s="271">
-        <v>7</v>
-      </c>
-      <c r="D196" s="272"/>
-      <c r="E196" s="290"/>
-      <c r="F196" s="301"/>
-    </row>
-    <row r="197" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B197" s="331"/>
-      <c r="C197" s="271">
-        <v>8</v>
-      </c>
-      <c r="D197" s="272"/>
-      <c r="E197" s="290"/>
-      <c r="F197" s="301"/>
-    </row>
-    <row r="198" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B198" s="331"/>
-      <c r="C198" s="271">
-        <v>9</v>
-      </c>
-      <c r="D198" s="272"/>
-      <c r="E198" s="290"/>
-      <c r="F198" s="301"/>
-    </row>
-    <row r="199" spans="2:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B199" s="332"/>
-      <c r="C199" s="274">
-        <v>10</v>
-      </c>
-      <c r="D199" s="275"/>
-      <c r="E199" s="291"/>
-      <c r="F199" s="306"/>
+      <c r="D199" s="273"/>
+      <c r="E199" s="289"/>
+      <c r="F199" s="327"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B180:B189"/>
-    <mergeCell ref="B190:B199"/>
-    <mergeCell ref="B4:B9"/>
-    <mergeCell ref="B132:B140"/>
-    <mergeCell ref="B141:B150"/>
-    <mergeCell ref="B129:B131"/>
-    <mergeCell ref="B50:B92"/>
-    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="F109:F118"/>
+    <mergeCell ref="M31:Q31"/>
+    <mergeCell ref="F180:F189"/>
+    <mergeCell ref="F190:F199"/>
+    <mergeCell ref="B99:B108"/>
+    <mergeCell ref="B37:B46"/>
+    <mergeCell ref="B27:B35"/>
+    <mergeCell ref="F171:F179"/>
+    <mergeCell ref="B171:B179"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="B161:B170"/>
     <mergeCell ref="F132:F140"/>
@@ -7330,15 +7261,15 @@
     <mergeCell ref="D51:E92"/>
     <mergeCell ref="B23:B25"/>
     <mergeCell ref="B17:B21"/>
-    <mergeCell ref="F109:F118"/>
-    <mergeCell ref="M31:Q31"/>
-    <mergeCell ref="F180:F189"/>
-    <mergeCell ref="F190:F199"/>
-    <mergeCell ref="B99:B108"/>
-    <mergeCell ref="B37:B46"/>
-    <mergeCell ref="B27:B35"/>
-    <mergeCell ref="F171:F179"/>
-    <mergeCell ref="B171:B179"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B180:B189"/>
+    <mergeCell ref="B190:B199"/>
+    <mergeCell ref="B4:B9"/>
+    <mergeCell ref="B132:B140"/>
+    <mergeCell ref="B141:B150"/>
+    <mergeCell ref="B129:B131"/>
+    <mergeCell ref="B50:B92"/>
+    <mergeCell ref="B11:B15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -7356,17 +7287,17 @@
   <sheetData>
     <row r="7" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="239" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="114" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="218" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="C10">
         <v>150000</v>
@@ -7374,7 +7305,7 @@
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="218" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="C11">
         <v>150000</v>
@@ -7382,7 +7313,7 @@
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="218" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="C12">
         <v>200000</v>
@@ -7396,32 +7327,32 @@
     </row>
     <row r="16" spans="2:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="240" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="218" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="218" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="218" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="218" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="238" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -7449,59 +7380,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A1" s="345"/>
-      <c r="B1" s="346"/>
-      <c r="C1" s="346"/>
-      <c r="D1" s="346"/>
-      <c r="E1" s="346"/>
-      <c r="F1" s="346"/>
-      <c r="G1" s="346"/>
+      <c r="A1" s="339"/>
+      <c r="B1" s="340"/>
+      <c r="C1" s="340"/>
+      <c r="D1" s="340"/>
+      <c r="E1" s="340"/>
+      <c r="F1" s="340"/>
+      <c r="G1" s="340"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A2" s="345"/>
-      <c r="B2" s="346"/>
-      <c r="C2" s="346"/>
-      <c r="D2" s="346"/>
-      <c r="E2" s="346"/>
-      <c r="F2" s="346"/>
-      <c r="G2" s="346"/>
+      <c r="A2" s="339"/>
+      <c r="B2" s="340"/>
+      <c r="C2" s="340"/>
+      <c r="D2" s="340"/>
+      <c r="E2" s="340"/>
+      <c r="F2" s="340"/>
+      <c r="G2" s="340"/>
     </row>
     <row r="3" spans="1:13" ht="49.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="347" t="s">
-        <v>120</v>
-      </c>
-      <c r="B3" s="346"/>
-      <c r="C3" s="346"/>
-      <c r="D3" s="346"/>
-      <c r="E3" s="346"/>
-      <c r="F3" s="346"/>
-      <c r="G3" s="346"/>
+      <c r="A3" s="346" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" s="340"/>
+      <c r="C3" s="340"/>
+      <c r="D3" s="340"/>
+      <c r="E3" s="340"/>
+      <c r="F3" s="340"/>
+      <c r="G3" s="340"/>
       <c r="H3" s="137"/>
       <c r="I3" s="137"/>
       <c r="J3" s="137"/>
       <c r="K3" s="137"/>
     </row>
     <row r="4" spans="1:13" ht="57" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="344" t="s">
-        <v>121</v>
-      </c>
-      <c r="B4" s="328"/>
-      <c r="C4" s="328"/>
-      <c r="D4" s="328"/>
-      <c r="E4" s="328"/>
-      <c r="F4" s="328"/>
-      <c r="G4" s="328"/>
+      <c r="A4" s="345" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="335"/>
+      <c r="C4" s="335"/>
+      <c r="D4" s="335"/>
+      <c r="E4" s="335"/>
+      <c r="F4" s="335"/>
+      <c r="G4" s="335"/>
       <c r="H4" s="146"/>
       <c r="I4" s="146"/>
       <c r="J4" s="146"/>
       <c r="K4" s="146"/>
     </row>
     <row r="5" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="341" t="s">
+      <c r="A5" s="350" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" s="341" t="s">
         <v>122</v>
-      </c>
-      <c r="B5" s="339" t="s">
-        <v>123</v>
       </c>
       <c r="C5" s="100" t="str">
         <f>Assumptions.1!J17</f>
@@ -7525,8 +7456,8 @@
       </c>
     </row>
     <row r="6" spans="1:13" s="3" customFormat="1" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="340"/>
-      <c r="B6" s="340"/>
+      <c r="A6" s="342"/>
+      <c r="B6" s="342"/>
       <c r="C6" s="130">
         <f>Assumptions.1!I17</f>
         <v>0</v>
@@ -7555,7 +7486,7 @@
     </row>
     <row r="8" spans="1:13" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B8" s="108"/>
       <c r="C8" s="6" t="e">
@@ -7588,7 +7519,7 @@
     </row>
     <row r="10" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C10" s="6">
         <f>Assumptions.1!F77</f>
@@ -7613,7 +7544,7 @@
     </row>
     <row r="11" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B11" s="108"/>
       <c r="C11" s="6" t="e">
@@ -7640,7 +7571,7 @@
     </row>
     <row r="12" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C12" s="2">
         <f>Assumptions.1!I12*Assumptions.1!F78</f>
@@ -7667,7 +7598,7 @@
     </row>
     <row r="13" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C13" s="7" t="e">
         <f>C8-C15</f>
@@ -7695,7 +7626,7 @@
     </row>
     <row r="15" spans="1:13" s="3" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C15" s="7" t="e">
         <f>C8*Assumptions.1!F57</f>
@@ -7728,7 +7659,7 @@
     </row>
     <row r="17" spans="1:13" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B17" s="108"/>
       <c r="C17" s="7" t="e">
@@ -7762,7 +7693,7 @@
     </row>
     <row r="19" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A19" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B19" s="108"/>
       <c r="C19" s="6" t="e">
@@ -7801,7 +7732,7 @@
     </row>
     <row r="21" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="15" t="e">
@@ -7841,7 +7772,7 @@
     </row>
     <row r="23" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A23" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="6">
@@ -7885,7 +7816,7 @@
     </row>
     <row r="25" spans="1:13" s="16" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A25" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C25" s="15" t="e">
         <f>C21-C23</f>
@@ -7928,7 +7859,7 @@
     </row>
     <row r="27" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A27" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="6">
@@ -7966,7 +7897,7 @@
     </row>
     <row r="29" spans="1:13" s="3" customFormat="1" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B29" s="9"/>
       <c r="C29" s="138" t="e">
@@ -7998,31 +7929,31 @@
     <row r="30" spans="1:13" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
-      <c r="C30" s="342" t="s">
+      <c r="C30" s="343" t="s">
+        <v>135</v>
+      </c>
+      <c r="D30" s="344"/>
+      <c r="E30" s="344"/>
+      <c r="F30" s="344"/>
+      <c r="G30" s="322"/>
+    </row>
+    <row r="31" spans="1:13" ht="48.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="345" t="s">
         <v>136</v>
       </c>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
-      <c r="G30" s="320"/>
-    </row>
-    <row r="31" spans="1:13" ht="48.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="344" t="s">
+      <c r="B31" s="335"/>
+      <c r="C31" s="335"/>
+      <c r="D31" s="335"/>
+      <c r="E31" s="335"/>
+      <c r="F31" s="335"/>
+      <c r="G31" s="335"/>
+    </row>
+    <row r="32" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A32" s="341" t="s">
         <v>137</v>
       </c>
-      <c r="B31" s="328"/>
-      <c r="C31" s="328"/>
-      <c r="D31" s="328"/>
-      <c r="E31" s="328"/>
-      <c r="F31" s="328"/>
-      <c r="G31" s="328"/>
-    </row>
-    <row r="32" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A32" s="339" t="s">
-        <v>138</v>
-      </c>
-      <c r="B32" s="339" t="s">
-        <v>123</v>
+      <c r="B32" s="341" t="s">
+        <v>122</v>
       </c>
       <c r="C32" s="102" t="str">
         <f>C5</f>
@@ -8046,8 +7977,8 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="95.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="340"/>
-      <c r="B33" s="340"/>
+      <c r="A33" s="342"/>
+      <c r="B33" s="342"/>
       <c r="C33" s="118">
         <f>C6</f>
         <v>0</v>
@@ -8071,7 +8002,7 @@
     </row>
     <row r="34" spans="1:10" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.5">
       <c r="A34" s="41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.5">
@@ -8079,7 +8010,7 @@
     </row>
     <row r="36" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A36" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B36" s="108"/>
       <c r="C36" s="48" t="e">
@@ -8108,19 +8039,19 @@
     </row>
     <row r="37" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A37" s="50" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B37" s="10"/>
     </row>
     <row r="38" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A38" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B38" s="1"/>
     </row>
     <row r="39" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A39" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B39" s="10"/>
       <c r="C39" s="46" t="e">
@@ -8147,7 +8078,7 @@
     </row>
     <row r="40" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A40" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B40" s="108"/>
       <c r="C40" s="6">
@@ -8199,17 +8130,17 @@
     <row r="43" spans="1:10" ht="25.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.5"/>
     <row r="44" spans="1:10" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="45" spans="1:10" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C45" s="336" t="s">
-        <v>136</v>
-      </c>
-      <c r="D45" s="337"/>
-      <c r="E45" s="337"/>
-      <c r="F45" s="337"/>
-      <c r="G45" s="338"/>
+      <c r="C45" s="347" t="s">
+        <v>135</v>
+      </c>
+      <c r="D45" s="348"/>
+      <c r="E45" s="348"/>
+      <c r="F45" s="348"/>
+      <c r="G45" s="349"/>
     </row>
     <row r="46" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A46" s="41" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.5">
@@ -8217,7 +8148,7 @@
     </row>
     <row r="48" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A48" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C48" s="6">
         <f>Depsch!N18</f>
@@ -8250,7 +8181,7 @@
     </row>
     <row r="50" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A50" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
@@ -8262,7 +8193,7 @@
     </row>
     <row r="52" spans="1:15" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A52" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B52" s="10"/>
       <c r="J52" s="106"/>
@@ -8302,7 +8233,7 @@
     </row>
     <row r="54" spans="1:15" ht="44.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A54" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B54" s="108"/>
       <c r="C54" s="6" t="e">
@@ -8330,7 +8261,7 @@
     </row>
     <row r="55" spans="1:15" ht="44.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A55" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B55" s="108"/>
       <c r="C55" s="6">
@@ -8353,7 +8284,7 @@
     </row>
     <row r="56" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A56" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B56" s="108"/>
       <c r="C56" s="6" t="e">
@@ -8407,13 +8338,13 @@
       <c r="M58" s="6"/>
     </row>
     <row r="59" spans="1:15" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C59" s="342" t="s">
-        <v>136</v>
-      </c>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
-      <c r="G59" s="320"/>
+      <c r="C59" s="343" t="s">
+        <v>135</v>
+      </c>
+      <c r="D59" s="344"/>
+      <c r="E59" s="344"/>
+      <c r="F59" s="344"/>
+      <c r="G59" s="322"/>
       <c r="I59" s="6"/>
       <c r="J59" s="6"/>
       <c r="K59" s="6"/>
@@ -8433,15 +8364,15 @@
       <c r="M60" s="84"/>
     </row>
     <row r="61" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="344" t="s">
-        <v>152</v>
-      </c>
-      <c r="B61" s="328"/>
-      <c r="C61" s="328"/>
-      <c r="D61" s="328"/>
-      <c r="E61" s="328"/>
-      <c r="F61" s="328"/>
-      <c r="G61" s="328"/>
+      <c r="A61" s="345" t="s">
+        <v>151</v>
+      </c>
+      <c r="B61" s="335"/>
+      <c r="C61" s="335"/>
+      <c r="D61" s="335"/>
+      <c r="E61" s="335"/>
+      <c r="F61" s="335"/>
+      <c r="G61" s="335"/>
     </row>
     <row r="62" spans="1:15" ht="95.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="51"/>
@@ -8470,7 +8401,7 @@
     <row r="63" spans="1:15" ht="25.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.5"/>
     <row r="64" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A64" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B64" s="108"/>
       <c r="C64" s="2">
@@ -8497,7 +8428,7 @@
     </row>
     <row r="65" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A65" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B65" s="108"/>
       <c r="C65" s="6">
@@ -8523,7 +8454,7 @@
     </row>
     <row r="66" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A66" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B66" s="108"/>
       <c r="C66" s="2">
@@ -8549,7 +8480,7 @@
     </row>
     <row r="67" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A67" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B67" s="108"/>
       <c r="C67" s="2">
@@ -8575,7 +8506,7 @@
     </row>
     <row r="68" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A68" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B68" s="108"/>
       <c r="C68" s="6" t="e">
@@ -8601,7 +8532,7 @@
     </row>
     <row r="69" spans="1:10" ht="53.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A69" s="107" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B69" s="108"/>
       <c r="C69" s="6" t="e">
@@ -8655,13 +8586,13 @@
       <c r="J74" s="6"/>
     </row>
     <row r="75" spans="1:10" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C75" s="336" t="s">
-        <v>136</v>
-      </c>
-      <c r="D75" s="337"/>
-      <c r="E75" s="337"/>
-      <c r="F75" s="337"/>
-      <c r="G75" s="338"/>
+      <c r="C75" s="347" t="s">
+        <v>135</v>
+      </c>
+      <c r="D75" s="348"/>
+      <c r="E75" s="348"/>
+      <c r="F75" s="348"/>
+      <c r="G75" s="349"/>
     </row>
     <row r="76" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="C76" s="3"/>
@@ -8669,14 +8600,14 @@
     </row>
     <row r="77" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A77" s="147" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A78" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C78" s="2">
         <f>Assumptions.1!I12</f>
@@ -8701,9 +8632,9 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.5">
       <c r="A80" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B80" s="247">
+        <v>160</v>
+      </c>
+      <c r="B80" s="245">
         <v>0.75</v>
       </c>
       <c r="C80" s="2">
@@ -8729,9 +8660,9 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A81" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B81" s="247">
+        <v>161</v>
+      </c>
+      <c r="B81" s="245">
         <v>0.5</v>
       </c>
       <c r="C81" s="6" t="e">
@@ -8764,7 +8695,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A83" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C83" s="6" t="e">
         <f>C80+C81</f>
@@ -8789,6 +8720,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="A61:G61"/>
+    <mergeCell ref="C45:G45"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B32:B33"/>
     <mergeCell ref="C30:G30"/>
@@ -8796,13 +8734,6 @@
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="A61:G61"/>
-    <mergeCell ref="C45:G45"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.19685039370078741" top="0.39370078740157483" bottom="0.3" header="0.23622047244094491" footer="0.16"/>
   <pageSetup scale="46" orientation="portrait" r:id="rId1"/>
@@ -8818,813 +8749,813 @@
   <dimension ref="A1:I43"/>
   <sheetFormatPr defaultColWidth="21.77734375" defaultRowHeight="25.8" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="49.44140625" style="374" customWidth="1"/>
-    <col min="2" max="2" width="26.44140625" style="374" customWidth="1"/>
-    <col min="3" max="3" width="23.77734375" style="374" customWidth="1"/>
-    <col min="4" max="4" width="25.44140625" style="374" customWidth="1"/>
-    <col min="5" max="5" width="24" style="374" customWidth="1"/>
-    <col min="6" max="6" width="28.21875" style="374" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32.21875" style="374" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.77734375" style="374" customWidth="1"/>
-    <col min="9" max="16384" width="21.77734375" style="374"/>
+    <col min="1" max="1" width="49.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.44140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="23.77734375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="25.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="24" style="2" customWidth="1"/>
+    <col min="6" max="6" width="28.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.77734375" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="21.77734375" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A1" s="372"/>
-      <c r="B1" s="373"/>
-      <c r="C1" s="373"/>
-      <c r="D1" s="373"/>
-      <c r="E1" s="373"/>
-      <c r="F1" s="373"/>
-      <c r="G1" s="373"/>
+      <c r="A1" s="339"/>
+      <c r="B1" s="340"/>
+      <c r="C1" s="340"/>
+      <c r="D1" s="340"/>
+      <c r="E1" s="340"/>
+      <c r="F1" s="340"/>
+      <c r="G1" s="340"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A2" s="372"/>
-      <c r="B2" s="373"/>
-      <c r="C2" s="373"/>
-      <c r="D2" s="373"/>
-      <c r="E2" s="373"/>
-      <c r="F2" s="373"/>
-      <c r="G2" s="373"/>
+      <c r="A2" s="339"/>
+      <c r="B2" s="340"/>
+      <c r="C2" s="340"/>
+      <c r="D2" s="340"/>
+      <c r="E2" s="340"/>
+      <c r="F2" s="340"/>
+      <c r="G2" s="340"/>
     </row>
     <row r="3" spans="1:7" ht="49.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="375" t="s">
+      <c r="A3" s="346" t="s">
+        <v>163</v>
+      </c>
+      <c r="B3" s="340"/>
+      <c r="C3" s="340"/>
+      <c r="D3" s="340"/>
+      <c r="E3" s="340"/>
+      <c r="F3" s="340"/>
+      <c r="G3" s="340"/>
+    </row>
+    <row r="4" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="353" t="s">
         <v>164</v>
       </c>
-      <c r="B3" s="373"/>
-      <c r="C3" s="373"/>
-      <c r="D3" s="373"/>
-      <c r="E3" s="373"/>
-      <c r="F3" s="373"/>
-      <c r="G3" s="373"/>
-    </row>
-    <row r="4" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="376" t="s">
-        <v>165</v>
-      </c>
-      <c r="B4" s="377"/>
-      <c r="C4" s="377"/>
-      <c r="D4" s="377"/>
-      <c r="E4" s="377"/>
-      <c r="F4" s="377"/>
-      <c r="G4" s="377"/>
+      <c r="B4" s="335"/>
+      <c r="C4" s="335"/>
+      <c r="D4" s="335"/>
+      <c r="E4" s="335"/>
+      <c r="F4" s="335"/>
+      <c r="G4" s="335"/>
     </row>
     <row r="5" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="378" t="s">
-        <v>122</v>
-      </c>
-      <c r="B5" s="379"/>
-      <c r="C5" s="380" t="str">
+      <c r="A5" s="350" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" s="298"/>
+      <c r="C5" s="100" t="str">
         <f>Assumptions.1!J17</f>
         <v>Estimated</v>
       </c>
-      <c r="D5" s="380" t="str">
+      <c r="D5" s="100" t="str">
         <f>Assumptions.1!J18</f>
         <v>Projected</v>
       </c>
-      <c r="E5" s="380" t="str">
+      <c r="E5" s="100" t="str">
         <f>Assumptions.1!J19</f>
         <v>Projected</v>
       </c>
-      <c r="F5" s="380" t="str">
+      <c r="F5" s="100" t="str">
         <f>Assumptions.1!J20</f>
         <v>Projected</v>
       </c>
-      <c r="G5" s="380" t="str">
+      <c r="G5" s="100" t="str">
         <f>Assumptions.1!J21</f>
         <v>Projected</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="385" customFormat="1" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="381"/>
-      <c r="B6" s="382"/>
-      <c r="C6" s="383">
+    <row r="6" spans="1:7" s="3" customFormat="1" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="342"/>
+      <c r="B6" s="299"/>
+      <c r="C6" s="130">
         <f>Assumptions.1!I17</f>
         <v>0</v>
       </c>
-      <c r="D6" s="384">
+      <c r="D6" s="101">
         <f>Assumptions.1!I18</f>
         <v>0</v>
       </c>
-      <c r="E6" s="384">
+      <c r="E6" s="101">
         <f>Assumptions.1!I19</f>
         <v>0</v>
       </c>
-      <c r="F6" s="384">
+      <c r="F6" s="101">
         <f>Assumptions.1!I20</f>
         <v>0</v>
       </c>
-      <c r="G6" s="384">
+      <c r="G6" s="101">
         <f>Assumptions.1!I21</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="385" customFormat="1" ht="42.45" customHeight="1" thickTop="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="374"/>
-      <c r="B7" s="374"/>
-      <c r="C7" s="386" t="s">
+    <row r="7" spans="1:7" s="3" customFormat="1" ht="42.45" customHeight="1" thickTop="1" x14ac:dyDescent="0.5">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="300" t="s">
+        <v>165</v>
+      </c>
+      <c r="D7" s="300" t="s">
+        <v>165</v>
+      </c>
+      <c r="E7" s="300" t="s">
+        <v>165</v>
+      </c>
+      <c r="F7" s="300" t="s">
+        <v>165</v>
+      </c>
+      <c r="G7" s="300" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="147" t="s">
         <v>166</v>
       </c>
-      <c r="D7" s="386" t="s">
-        <v>166</v>
-      </c>
-      <c r="E7" s="386" t="s">
-        <v>166</v>
-      </c>
-      <c r="F7" s="386" t="s">
-        <v>166</v>
-      </c>
-      <c r="G7" s="386" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="385" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="387" t="s">
+      <c r="B8" s="2"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B8" s="374"/>
-      <c r="C8" s="388"/>
-      <c r="D8" s="388"/>
-    </row>
-    <row r="9" spans="1:7" s="385" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="374" t="s">
+      <c r="B9" s="2"/>
+      <c r="C9" s="301" t="e">
+        <f>wc!C8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D9" s="301" t="e">
+        <f>wc!D8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E9" s="301" t="e">
+        <f>wc!E8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F9" s="301" t="e">
+        <f>wc!F8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G9" s="301" t="e">
+        <f>wc!G8</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A10" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="301" t="e">
+        <f>wc!C11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D10" s="301" t="e">
+        <f>wc!D11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E10" s="301" t="e">
+        <f>wc!E11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F10" s="301" t="e">
+        <f>wc!F11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G10" s="301" t="e">
+        <f>wc!G11</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A11" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B9" s="374"/>
-      <c r="C9" s="398" t="e">
-        <f>wc!C8</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D9" s="398" t="e">
-        <f>wc!D8</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E9" s="398" t="e">
-        <f>wc!E8</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F9" s="398" t="e">
-        <f>wc!F8</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G9" s="398" t="e">
-        <f>wc!G8</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="374" t="s">
-        <v>125</v>
-      </c>
-      <c r="C10" s="398" t="e">
-        <f>wc!C11</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D10" s="398" t="e">
-        <f>wc!D11</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E10" s="398" t="e">
-        <f>wc!E11</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F10" s="398" t="e">
-        <f>wc!F11</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G10" s="398" t="e">
-        <f>wc!G11</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="374" t="s">
+      <c r="C11" s="302">
+        <f>wc!C12</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="302">
+        <f>wc!D12</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="302">
+        <f>wc!E12</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="302">
+        <f>wc!F12</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="302">
+        <f>wc!G12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C11" s="399">
-        <f>wc!C12</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="399">
-        <f>wc!D12</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="399">
-        <f>wc!E12</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="399">
-        <f>wc!F12</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="399">
-        <f>wc!G12</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" s="385" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="374" t="s">
+      <c r="B12" s="2"/>
+      <c r="C12" s="301" t="e">
+        <f>wc!C17</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D12" s="301" t="e">
+        <f>wc!D17</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E12" s="301" t="e">
+        <f>wc!E17</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F12" s="301" t="e">
+        <f>wc!F17</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G12" s="301" t="e">
+        <f>wc!G17</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="302">
+        <f>wc!C64</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="302">
+        <f>wc!D64</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="302">
+        <f>wc!E64</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="302">
+        <f>wc!F64</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="302">
+        <f>wc!G64</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C14" s="301">
+        <f>wc!C65</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="301">
+        <f>wc!D65</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="301">
+        <f>wc!E65</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="301">
+        <f>wc!F65</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="301">
+        <f>wc!G65</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A15" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C15" s="302">
+        <f>wc!C66</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="302">
+        <f>wc!D66</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="302">
+        <f>wc!E66</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="302">
+        <f>wc!F66</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="302">
+        <f>wc!G66</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A16" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C16" s="301" t="e">
+        <f>wc!C68</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D16" s="301" t="e">
+        <f>wc!D68</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E16" s="301" t="e">
+        <f>wc!E68</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F16" s="301" t="e">
+        <f>wc!F68</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G16" s="301" t="e">
+        <f>wc!G68</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="66.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A17" s="107" t="s">
+        <v>157</v>
+      </c>
+      <c r="B17" s="107"/>
+      <c r="C17" s="301" t="e">
+        <f>wc!C69</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D17" s="301" t="e">
+        <f>wc!D69</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E17" s="301" t="e">
+        <f>wc!E69</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F17" s="301" t="e">
+        <f>wc!F69</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G17" s="301" t="e">
+        <f>wc!G69</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A18" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B12" s="374"/>
-      <c r="C12" s="398" t="e">
-        <f>wc!C17</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D12" s="398" t="e">
-        <f>wc!D17</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E12" s="398" t="e">
-        <f>wc!E17</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F12" s="398" t="e">
-        <f>wc!F17</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G12" s="398" t="e">
-        <f>wc!G17</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" s="385" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="374" t="s">
-        <v>153</v>
-      </c>
-      <c r="B13" s="374"/>
-      <c r="C13" s="399">
-        <f>wc!C64</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="399">
-        <f>wc!D64</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="399">
-        <f>wc!E64</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="399">
-        <f>wc!F64</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="399">
-        <f>wc!G64</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="374" t="s">
-        <v>154</v>
-      </c>
-      <c r="C14" s="398">
-        <f>wc!C65</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="398">
-        <f>wc!D65</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="398">
-        <f>wc!E65</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="398">
-        <f>wc!F65</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="398">
-        <f>wc!G65</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="374" t="s">
-        <v>155</v>
-      </c>
-      <c r="C15" s="399">
-        <f>wc!C66</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="399">
-        <f>wc!D66</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="399">
-        <f>wc!E66</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="399">
-        <f>wc!F66</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="399">
-        <f>wc!G66</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="374" t="s">
-        <v>157</v>
-      </c>
-      <c r="C16" s="398" t="e">
-        <f>wc!C68</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D16" s="398" t="e">
-        <f>wc!D68</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E16" s="398" t="e">
-        <f>wc!E68</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F16" s="398" t="e">
-        <f>wc!F68</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G16" s="398" t="e">
-        <f>wc!G68</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="66.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A17" s="390" t="s">
-        <v>158</v>
-      </c>
-      <c r="B17" s="390"/>
-      <c r="C17" s="398" t="e">
-        <f>wc!C69</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D17" s="398" t="e">
-        <f>wc!D69</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E17" s="398" t="e">
-        <f>wc!E69</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F17" s="398" t="e">
-        <f>wc!F69</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G17" s="398" t="e">
-        <f>wc!G69</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" s="385" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="374" t="s">
+      <c r="B18" s="2"/>
+      <c r="C18" s="301">
+        <f>wc!C27</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="301">
+        <f>wc!D27</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="301">
+        <f>wc!E27</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="301">
+        <f>wc!F27</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="301">
+        <f>wc!G27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A19" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B18" s="374"/>
-      <c r="C18" s="398">
-        <f>wc!C27</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="398">
-        <f>wc!D27</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="398">
-        <f>wc!E27</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="398">
-        <f>wc!F27</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="398">
-        <f>wc!G27</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" s="385" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A19" s="374" t="s">
+      <c r="B19" s="2"/>
+      <c r="C19" s="301" t="e">
+        <f>plbs!C35</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D19" s="301" t="e">
+        <f>plbs!D35</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E19" s="301" t="e">
+        <f>plbs!E35</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F19" s="301" t="e">
+        <f>plbs!F35</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G19" s="301" t="e">
+        <f>plbs!G35</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="301"/>
+      <c r="D20" s="301"/>
+      <c r="E20" s="301"/>
+      <c r="F20" s="301"/>
+      <c r="G20" s="301"/>
+    </row>
+    <row r="21" spans="1:9" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A21" s="147" t="s">
         <v>172</v>
       </c>
-      <c r="B19" s="374"/>
-      <c r="C19" s="398" t="e">
-        <f>plbs!C35</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D19" s="398" t="e">
-        <f>plbs!D35</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E19" s="398" t="e">
-        <f>plbs!E35</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F19" s="398" t="e">
-        <f>plbs!F35</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G19" s="398" t="e">
-        <f>plbs!G35</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" s="385" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A20" s="374"/>
-      <c r="B20" s="374"/>
-      <c r="C20" s="398"/>
-      <c r="D20" s="398"/>
-      <c r="E20" s="398"/>
-      <c r="F20" s="398"/>
-      <c r="G20" s="398"/>
-    </row>
-    <row r="21" spans="1:9" s="385" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A21" s="387" t="s">
+      <c r="B21" s="2"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+    </row>
+    <row r="22" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A22" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C22" s="301">
+        <f>wc!C40</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="301">
+        <f>wc!D40</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="301">
+        <f>wc!E40</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="301">
+        <f>wc!F40</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="301">
+        <f>wc!G40</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="106"/>
+    </row>
+    <row r="23" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A23" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C23" s="301" t="e">
+        <f>wc!C54</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D23" s="301" t="e">
+        <f>wc!D54</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E23" s="301" t="e">
+        <f>wc!E54</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F23" s="301" t="e">
+        <f>wc!F54</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G23" s="301" t="e">
+        <f>wc!G54</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I23" s="6"/>
+    </row>
+    <row r="24" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A24" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C24" s="301">
+        <f>SUM(Depsch!C18:I18)</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="301">
+        <f>SUM(Depsch!C25:I25)</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="301">
+        <f>SUM(Depsch!C32:I32)</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="301">
+        <f>SUM(Depsch!C39:I39)</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="301">
+        <f>SUM(Depsch!C46:I46)</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="6"/>
+    </row>
+    <row r="25" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A25" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C25" s="301">
+        <f>wc!C55</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="301">
+        <f>wc!D55</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="301">
+        <f>wc!E55</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="301">
+        <f>wc!F55</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="301">
+        <f>wc!G55</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="106"/>
+    </row>
+    <row r="26" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A26" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C26" s="301" t="e">
+        <f>wc!C56</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D26" s="302" t="e">
+        <f>wc!D56</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E26" s="302" t="e">
+        <f>wc!E56</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F26" s="302" t="e">
+        <f>wc!F56</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G26" s="302" t="e">
+        <f>wc!G56</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I26" s="84"/>
+    </row>
+    <row r="28" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A28" s="147" t="s">
         <v>173</v>
       </c>
-      <c r="B21" s="374"/>
-      <c r="C21" s="389"/>
-      <c r="D21" s="389"/>
-      <c r="E21" s="389"/>
-      <c r="F21" s="389"/>
-      <c r="G21" s="389"/>
-    </row>
-    <row r="22" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A22" s="374" t="s">
-        <v>144</v>
-      </c>
-      <c r="C22" s="398">
-        <f>wc!C40</f>
-        <v>0</v>
-      </c>
-      <c r="D22" s="398">
-        <f>wc!D40</f>
-        <v>0</v>
-      </c>
-      <c r="E22" s="398">
-        <f>wc!E40</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="398">
-        <f>wc!F40</f>
-        <v>0</v>
-      </c>
-      <c r="G22" s="398">
-        <f>wc!G40</f>
-        <v>0</v>
-      </c>
-      <c r="I22" s="391"/>
-    </row>
-    <row r="23" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A23" s="374" t="s">
-        <v>149</v>
-      </c>
-      <c r="C23" s="398" t="e">
-        <f>wc!C54</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D23" s="398" t="e">
-        <f>wc!D54</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E23" s="398" t="e">
-        <f>wc!E54</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F23" s="398" t="e">
-        <f>wc!F54</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G23" s="398" t="e">
-        <f>wc!G54</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I23" s="389"/>
-    </row>
-    <row r="24" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A24" s="374" t="s">
-        <v>147</v>
-      </c>
-      <c r="C24" s="398">
-        <f>SUM(Depsch!C18:I18)</f>
-        <v>0</v>
-      </c>
-      <c r="D24" s="398">
-        <f>SUM(Depsch!C25:I25)</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="398">
-        <f>SUM(Depsch!C32:I32)</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="398">
-        <f>SUM(Depsch!C39:I39)</f>
-        <v>0</v>
-      </c>
-      <c r="G24" s="398">
-        <f>SUM(Depsch!C46:I46)</f>
-        <v>0</v>
-      </c>
-      <c r="I24" s="389"/>
-    </row>
-    <row r="25" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A25" s="374" t="s">
-        <v>150</v>
-      </c>
-      <c r="C25" s="398">
-        <f>wc!C55</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="398">
-        <f>wc!D55</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="398">
-        <f>wc!E55</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="398">
-        <f>wc!F55</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="398">
-        <f>wc!G55</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="391"/>
-    </row>
-    <row r="26" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A26" s="374" t="s">
-        <v>151</v>
-      </c>
-      <c r="C26" s="398" t="e">
-        <f>wc!C56</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D26" s="399" t="e">
-        <f>wc!D56</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E26" s="399" t="e">
-        <f>wc!E56</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F26" s="399" t="e">
-        <f>wc!F56</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G26" s="399" t="e">
-        <f>wc!G56</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I26" s="392"/>
-    </row>
-    <row r="28" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A28" s="387" t="s">
+      <c r="B28" s="3"/>
+    </row>
+    <row r="29" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A29" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B28" s="385"/>
-    </row>
-    <row r="29" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A29" s="374" t="s">
-        <v>175</v>
-      </c>
-      <c r="C29" s="392" t="str">
+      <c r="C29" s="84" t="str">
         <f>IFERROR(RATIO!C36, "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="D29" s="392" t="str">
+      <c r="D29" s="84" t="str">
         <f>IFERROR(RATIO!D36, "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="E29" s="392" t="str">
+      <c r="E29" s="84" t="str">
         <f>IFERROR(RATIO!E36, "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="F29" s="392" t="str">
+      <c r="F29" s="84" t="str">
         <f>IFERROR(RATIO!F36, "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="G29" s="392" t="str">
+      <c r="G29" s="84" t="str">
         <f>IFERROR(RATIO!G36, "N/A")</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A30" s="374" t="s">
-        <v>176</v>
-      </c>
-      <c r="C30" s="392" t="str">
+      <c r="A30" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C30" s="84" t="str">
         <f>IFERROR(RATIO!C44, "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="D30" s="392" t="str">
+      <c r="D30" s="84" t="str">
         <f>IFERROR(RATIO!D44, "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="E30" s="392" t="str">
+      <c r="E30" s="84" t="str">
         <f>IFERROR(RATIO!E44, "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="F30" s="392" t="str">
+      <c r="F30" s="84" t="str">
         <f>IFERROR(RATIO!F44, "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="G30" s="392" t="str">
+      <c r="G30" s="84" t="str">
         <f>IFERROR(RATIO!G44, "N/A")</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A31" s="374" t="s">
-        <v>177</v>
-      </c>
-      <c r="C31" s="389" t="str">
+      <c r="A31" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C31" s="6" t="str">
         <f>IFERROR(RATIO!C27, "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="D31" s="389" t="str">
+      <c r="D31" s="6" t="str">
         <f>IFERROR(RATIO!D27, "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="E31" s="389" t="str">
+      <c r="E31" s="6" t="str">
         <f>IFERROR(RATIO!E27, "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="F31" s="389" t="str">
+      <c r="F31" s="6" t="str">
         <f>IFERROR(RATIO!F27, "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="G31" s="389" t="str">
+      <c r="G31" s="6" t="str">
         <f>IFERROR(RATIO!G27, "N/A")</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A32" s="374" t="s">
-        <v>178</v>
-      </c>
-      <c r="C32" s="392" t="str">
+      <c r="A32" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C32" s="84" t="str">
         <f>IFERROR(RATIO!C11, "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="D32" s="392" t="str">
+      <c r="D32" s="84" t="str">
         <f>IFERROR(RATIO!D11, "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="E32" s="392" t="str">
+      <c r="E32" s="84" t="str">
         <f>IFERROR(RATIO!E11, "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="F32" s="392" t="str">
+      <c r="F32" s="84" t="str">
         <f>IFERROR(RATIO!F11, "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="G32" s="392" t="str">
+      <c r="G32" s="84" t="str">
         <f>IFERROR(RATIO!G11, "N/A")</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A33" s="374" t="s">
-        <v>179</v>
-      </c>
-      <c r="C33" s="392" t="str">
+      <c r="A33" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C33" s="84" t="str">
         <f>IFERROR(RATIO!C87, "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="D33" s="392" t="str">
+      <c r="D33" s="84" t="str">
         <f>IFERROR(RATIO!D87, "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="E33" s="392" t="str">
+      <c r="E33" s="84" t="str">
         <f>IFERROR(RATIO!E87, "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="F33" s="392" t="str">
+      <c r="F33" s="84" t="str">
         <f>IFERROR(RATIO!F87, "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="G33" s="392" t="str">
+      <c r="G33" s="84" t="str">
         <f>IFERROR(RATIO!G87, "N/A")</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="C34" s="392"/>
-      <c r="D34" s="392"/>
-      <c r="E34" s="392"/>
-      <c r="F34" s="392"/>
-      <c r="G34" s="392"/>
+      <c r="C34" s="84"/>
+      <c r="D34" s="84"/>
+      <c r="E34" s="84"/>
+      <c r="F34" s="84"/>
+      <c r="G34" s="84"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A35" s="387" t="s">
+      <c r="A35" s="147" t="s">
+        <v>179</v>
+      </c>
+      <c r="C35" s="84"/>
+      <c r="D35" s="84"/>
+      <c r="E35" s="84"/>
+      <c r="F35" s="84"/>
+      <c r="G35" s="84"/>
+    </row>
+    <row r="36" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A36" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C35" s="392"/>
-      <c r="D35" s="392"/>
-      <c r="E35" s="392"/>
-      <c r="F35" s="392"/>
-      <c r="G35" s="392"/>
-    </row>
-    <row r="36" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A36" s="374" t="s">
+      <c r="C36" s="301" t="e">
+        <f>'MPBF '!B27</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D36" s="301" t="e">
+        <f>'MPBF '!C27</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E36" s="301" t="e">
+        <f>'MPBF '!D27</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F36" s="301" t="e">
+        <f>'MPBF '!E27</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G36" s="301" t="e">
+        <f>'MPBF '!F27</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A37" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C36" s="398" t="e">
-        <f>'MPBF '!B27</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D36" s="398" t="e">
-        <f>'MPBF '!C27</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E36" s="398" t="e">
-        <f>'MPBF '!D27</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F36" s="398" t="e">
-        <f>'MPBF '!E27</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G36" s="398" t="e">
-        <f>'MPBF '!F27</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A37" s="374" t="s">
+      <c r="C37" s="301" t="e">
+        <f>'MPBF '!B50</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D37" s="301" t="e">
+        <f>'MPBF '!C50</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E37" s="301" t="e">
+        <f>'MPBF '!D50</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F37" s="301" t="e">
+        <f>'MPBF '!E50</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G37" s="301" t="e">
+        <f>'MPBF '!F50</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A38" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C37" s="398" t="e">
-        <f>'MPBF '!B50</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D37" s="398" t="e">
-        <f>'MPBF '!C50</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E37" s="398" t="e">
-        <f>'MPBF '!D50</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F37" s="398" t="e">
-        <f>'MPBF '!E50</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G37" s="398" t="e">
-        <f>'MPBF '!F50</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A38" s="374" t="s">
-        <v>183</v>
-      </c>
-      <c r="C38" s="398" t="e">
+      <c r="C38" s="301" t="e">
         <f>Nayak!C23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D38" s="398" t="e">
+      <c r="D38" s="301" t="e">
         <f>Nayak!D23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E38" s="398" t="e">
+      <c r="E38" s="301" t="e">
         <f>Nayak!E23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F38" s="398" t="e">
+      <c r="F38" s="301" t="e">
         <f>Nayak!F23</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G38" s="398" t="e">
+      <c r="G38" s="301" t="e">
         <f>Nayak!G23</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="393"/>
-      <c r="B39" s="393"/>
-      <c r="C39" s="393"/>
-      <c r="D39" s="393"/>
-      <c r="E39" s="393"/>
-      <c r="F39" s="393"/>
-      <c r="G39" s="393"/>
+      <c r="A39" s="12"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="C40" s="394"/>
-      <c r="D40" s="395"/>
+      <c r="C40" s="351"/>
+      <c r="D40" s="352"/>
     </row>
     <row r="41" spans="1:7" ht="25.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C41" s="396"/>
-      <c r="D41" s="397"/>
+      <c r="C41" s="307"/>
+      <c r="D41" s="322"/>
     </row>
     <row r="43" spans="1:7" ht="31.05" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="375"/>
-      <c r="B43" s="373"/>
-      <c r="C43" s="373"/>
-      <c r="D43" s="373"/>
-      <c r="E43" s="373"/>
-      <c r="F43" s="373"/>
-      <c r="G43" s="373"/>
+      <c r="A43" s="346"/>
+      <c r="B43" s="340"/>
+      <c r="C43" s="340"/>
+      <c r="D43" s="340"/>
+      <c r="E43" s="340"/>
+      <c r="F43" s="340"/>
+      <c r="G43" s="340"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -9700,75 +9631,79 @@
       <c r="C5" s="73"/>
       <c r="K5" s="73"/>
       <c r="L5" s="74"/>
+      <c r="T5" s="378"/>
+      <c r="U5" s="378"/>
+      <c r="V5" s="378"/>
+      <c r="W5" s="378"/>
     </row>
     <row r="6" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B6" s="72"/>
       <c r="C6" s="73"/>
-      <c r="D6" s="348" t="s">
-        <v>184</v>
-      </c>
-      <c r="E6" s="349"/>
-      <c r="F6" s="349"/>
-      <c r="G6" s="349"/>
-      <c r="H6" s="349"/>
-      <c r="I6" s="349"/>
-      <c r="J6" s="349"/>
-      <c r="K6" s="248"/>
+      <c r="D6" s="354" t="s">
+        <v>183</v>
+      </c>
+      <c r="E6" s="355"/>
+      <c r="F6" s="355"/>
+      <c r="G6" s="355"/>
+      <c r="H6" s="355"/>
+      <c r="I6" s="355"/>
+      <c r="J6" s="355"/>
+      <c r="K6" s="246"/>
       <c r="L6" s="74"/>
-      <c r="T6" s="65" t="s">
-        <v>185</v>
-      </c>
+      <c r="T6" s="379"/>
+      <c r="U6" s="378"/>
+      <c r="V6" s="378"/>
+      <c r="W6" s="378"/>
     </row>
     <row r="7" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B7" s="72"/>
       <c r="C7" s="73"/>
       <c r="K7" s="73"/>
       <c r="L7" s="74"/>
+      <c r="T7" s="378"/>
+      <c r="U7" s="378"/>
+      <c r="V7" s="378"/>
+      <c r="W7" s="378"/>
     </row>
     <row r="8" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B8" s="72"/>
       <c r="C8" s="73"/>
-      <c r="E8" s="348" t="s">
-        <v>186</v>
-      </c>
-      <c r="F8" s="349"/>
-      <c r="G8" s="349"/>
-      <c r="H8" s="349"/>
-      <c r="I8" s="349"/>
+      <c r="E8" s="354" t="s">
+        <v>184</v>
+      </c>
+      <c r="F8" s="355"/>
+      <c r="G8" s="355"/>
+      <c r="H8" s="355"/>
+      <c r="I8" s="355"/>
       <c r="J8" s="64"/>
-      <c r="K8" s="248"/>
+      <c r="K8" s="246"/>
       <c r="L8" s="74"/>
-      <c r="T8" s="243" t="s">
-        <v>187</v>
-      </c>
-      <c r="U8" s="243" t="s">
-        <v>188</v>
-      </c>
-      <c r="V8" s="65"/>
+      <c r="T8" s="379"/>
+      <c r="U8" s="379"/>
+      <c r="V8" s="379"/>
+      <c r="W8" s="378"/>
       <c r="X8" s="65"/>
       <c r="Y8" s="65"/>
     </row>
     <row r="9" spans="2:25" ht="38.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B9" s="72"/>
       <c r="C9" s="73"/>
-      <c r="D9" s="348">
+      <c r="D9" s="354">
         <f>Assumptions.1!I4</f>
         <v>0</v>
       </c>
-      <c r="E9" s="349"/>
-      <c r="F9" s="349"/>
-      <c r="G9" s="349"/>
-      <c r="H9" s="349"/>
-      <c r="I9" s="349"/>
-      <c r="J9" s="349"/>
-      <c r="K9" s="248"/>
+      <c r="E9" s="355"/>
+      <c r="F9" s="355"/>
+      <c r="G9" s="355"/>
+      <c r="H9" s="355"/>
+      <c r="I9" s="355"/>
+      <c r="J9" s="355"/>
+      <c r="K9" s="246"/>
       <c r="L9" s="74"/>
-      <c r="T9" s="244" t="s">
-        <v>189</v>
-      </c>
-      <c r="U9" s="244" t="s">
-        <v>190</v>
-      </c>
+      <c r="T9" s="378"/>
+      <c r="U9" s="378"/>
+      <c r="V9" s="378"/>
+      <c r="W9" s="378"/>
     </row>
     <row r="10" spans="2:25" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="72"/>
@@ -9780,48 +9715,42 @@
       <c r="H10" s="64"/>
       <c r="I10" s="64"/>
       <c r="J10" s="64"/>
-      <c r="K10" s="248"/>
+      <c r="K10" s="246"/>
       <c r="L10" s="74"/>
-      <c r="T10" s="244" t="s">
-        <v>15</v>
-      </c>
-      <c r="U10" s="244" t="s">
-        <v>191</v>
-      </c>
+      <c r="T10" s="378"/>
+      <c r="U10" s="378"/>
+      <c r="V10" s="378"/>
+      <c r="W10" s="378"/>
     </row>
     <row r="11" spans="2:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B11" s="72"/>
       <c r="C11" s="73"/>
       <c r="K11" s="73"/>
       <c r="L11" s="74"/>
-      <c r="T11" s="244" t="s">
-        <v>192</v>
-      </c>
-      <c r="U11" s="244" t="s">
-        <v>193</v>
-      </c>
+      <c r="T11" s="378"/>
+      <c r="U11" s="378"/>
+      <c r="V11" s="378"/>
+      <c r="W11" s="378"/>
     </row>
     <row r="12" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B12" s="72"/>
       <c r="C12" s="73"/>
-      <c r="D12" s="348">
+      <c r="D12" s="354">
         <f>Assumptions.1!I6</f>
         <v>0</v>
       </c>
-      <c r="E12" s="349"/>
-      <c r="F12" s="349"/>
-      <c r="G12" s="349"/>
-      <c r="H12" s="349"/>
-      <c r="I12" s="349"/>
-      <c r="J12" s="349"/>
-      <c r="K12" s="248"/>
+      <c r="E12" s="355"/>
+      <c r="F12" s="355"/>
+      <c r="G12" s="355"/>
+      <c r="H12" s="355"/>
+      <c r="I12" s="355"/>
+      <c r="J12" s="355"/>
+      <c r="K12" s="246"/>
       <c r="L12" s="74"/>
-      <c r="T12" s="244" t="s">
-        <v>194</v>
-      </c>
-      <c r="U12" s="244" t="s">
-        <v>195</v>
-      </c>
+      <c r="T12" s="378"/>
+      <c r="U12" s="378"/>
+      <c r="V12" s="378"/>
+      <c r="W12" s="378"/>
     </row>
     <row r="13" spans="2:25" ht="23.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B13" s="72"/>
@@ -9833,147 +9762,171 @@
       <c r="I13" s="67"/>
       <c r="K13" s="73"/>
       <c r="L13" s="74"/>
+      <c r="T13" s="378"/>
+      <c r="U13" s="378"/>
+      <c r="V13" s="378"/>
+      <c r="W13" s="378"/>
     </row>
     <row r="14" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B14" s="72"/>
       <c r="C14" s="73"/>
       <c r="K14" s="73"/>
       <c r="L14" s="74"/>
+      <c r="T14" s="378"/>
+      <c r="U14" s="378"/>
+      <c r="V14" s="378"/>
+      <c r="W14" s="378"/>
     </row>
     <row r="15" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B15" s="72"/>
       <c r="C15" s="73"/>
       <c r="K15" s="73"/>
       <c r="L15" s="74"/>
+      <c r="T15" s="378"/>
+      <c r="U15" s="378"/>
+      <c r="V15" s="378"/>
+      <c r="W15" s="378"/>
     </row>
     <row r="16" spans="2:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="72"/>
       <c r="C16" s="73"/>
-      <c r="D16" s="352">
+      <c r="D16" s="359">
         <f>Assumptions.1!I9</f>
         <v>0</v>
       </c>
-      <c r="E16" s="349"/>
-      <c r="F16" s="349"/>
-      <c r="G16" s="349"/>
-      <c r="H16" s="349"/>
-      <c r="I16" s="349"/>
-      <c r="J16" s="349"/>
-      <c r="K16" s="246"/>
+      <c r="E16" s="355"/>
+      <c r="F16" s="355"/>
+      <c r="G16" s="355"/>
+      <c r="H16" s="355"/>
+      <c r="I16" s="355"/>
+      <c r="J16" s="355"/>
+      <c r="K16" s="244"/>
       <c r="L16" s="76"/>
-    </row>
-    <row r="17" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="T16" s="378"/>
+      <c r="U16" s="378"/>
+      <c r="V16" s="378"/>
+      <c r="W16" s="378"/>
+    </row>
+    <row r="17" spans="2:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="72"/>
       <c r="C17" s="73"/>
-      <c r="D17" s="349"/>
-      <c r="E17" s="349"/>
-      <c r="F17" s="349"/>
-      <c r="G17" s="349"/>
-      <c r="H17" s="349"/>
-      <c r="I17" s="349"/>
-      <c r="J17" s="349"/>
-      <c r="K17" s="246"/>
+      <c r="D17" s="355"/>
+      <c r="E17" s="355"/>
+      <c r="F17" s="355"/>
+      <c r="G17" s="355"/>
+      <c r="H17" s="355"/>
+      <c r="I17" s="355"/>
+      <c r="J17" s="355"/>
+      <c r="K17" s="244"/>
       <c r="L17" s="76"/>
-    </row>
-    <row r="18" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="T17" s="378"/>
+      <c r="U17" s="378"/>
+      <c r="V17" s="378"/>
+      <c r="W17" s="378"/>
+    </row>
+    <row r="18" spans="2:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="72"/>
       <c r="C18" s="73"/>
-      <c r="D18" s="349"/>
-      <c r="E18" s="349"/>
-      <c r="F18" s="349"/>
-      <c r="G18" s="349"/>
-      <c r="H18" s="349"/>
-      <c r="I18" s="349"/>
-      <c r="J18" s="349"/>
-      <c r="K18" s="246"/>
+      <c r="D18" s="355"/>
+      <c r="E18" s="355"/>
+      <c r="F18" s="355"/>
+      <c r="G18" s="355"/>
+      <c r="H18" s="355"/>
+      <c r="I18" s="355"/>
+      <c r="J18" s="355"/>
+      <c r="K18" s="244"/>
       <c r="L18" s="76"/>
-    </row>
-    <row r="19" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="T18" s="378"/>
+      <c r="U18" s="378"/>
+      <c r="V18" s="378"/>
+      <c r="W18" s="378"/>
+    </row>
+    <row r="19" spans="2:23" ht="12.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B19" s="72"/>
       <c r="C19" s="73"/>
-      <c r="D19" s="349"/>
-      <c r="E19" s="349"/>
-      <c r="F19" s="349"/>
-      <c r="G19" s="349"/>
-      <c r="H19" s="349"/>
-      <c r="I19" s="349"/>
-      <c r="J19" s="349"/>
-      <c r="K19" s="246"/>
+      <c r="D19" s="355"/>
+      <c r="E19" s="355"/>
+      <c r="F19" s="355"/>
+      <c r="G19" s="355"/>
+      <c r="H19" s="355"/>
+      <c r="I19" s="355"/>
+      <c r="J19" s="355"/>
+      <c r="K19" s="244"/>
       <c r="L19" s="76"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B20" s="72"/>
       <c r="C20" s="73"/>
-      <c r="D20" s="351">
+      <c r="D20" s="358">
         <f>Assumptions.1!I7</f>
         <v>0</v>
       </c>
-      <c r="E20" s="349"/>
-      <c r="F20" s="349"/>
-      <c r="G20" s="349"/>
-      <c r="H20" s="349"/>
-      <c r="I20" s="349"/>
-      <c r="J20" s="349"/>
-      <c r="K20" s="246"/>
+      <c r="E20" s="355"/>
+      <c r="F20" s="355"/>
+      <c r="G20" s="355"/>
+      <c r="H20" s="355"/>
+      <c r="I20" s="355"/>
+      <c r="J20" s="355"/>
+      <c r="K20" s="244"/>
       <c r="L20" s="74"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B21" s="72"/>
       <c r="C21" s="73"/>
-      <c r="D21" s="349"/>
-      <c r="E21" s="349"/>
-      <c r="F21" s="349"/>
-      <c r="G21" s="349"/>
-      <c r="H21" s="349"/>
-      <c r="I21" s="349"/>
-      <c r="J21" s="349"/>
-      <c r="K21" s="246"/>
+      <c r="D21" s="355"/>
+      <c r="E21" s="355"/>
+      <c r="F21" s="355"/>
+      <c r="G21" s="355"/>
+      <c r="H21" s="355"/>
+      <c r="I21" s="355"/>
+      <c r="J21" s="355"/>
+      <c r="K21" s="244"/>
       <c r="L21" s="74"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B22" s="72"/>
       <c r="C22" s="73"/>
-      <c r="D22" s="349"/>
-      <c r="E22" s="349"/>
-      <c r="F22" s="349"/>
-      <c r="G22" s="349"/>
-      <c r="H22" s="349"/>
-      <c r="I22" s="349"/>
-      <c r="J22" s="349"/>
-      <c r="K22" s="246"/>
+      <c r="D22" s="355"/>
+      <c r="E22" s="355"/>
+      <c r="F22" s="355"/>
+      <c r="G22" s="355"/>
+      <c r="H22" s="355"/>
+      <c r="I22" s="355"/>
+      <c r="J22" s="355"/>
+      <c r="K22" s="244"/>
       <c r="L22" s="74"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B23" s="72"/>
       <c r="C23" s="73"/>
-      <c r="E23" s="350"/>
-      <c r="F23" s="349"/>
+      <c r="E23" s="357"/>
+      <c r="F23" s="355"/>
       <c r="G23" s="65"/>
       <c r="H23" s="65"/>
       <c r="I23" s="65"/>
       <c r="J23" s="64"/>
-      <c r="K23" s="248"/>
+      <c r="K23" s="246"/>
       <c r="L23" s="74"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B24" s="72"/>
       <c r="C24" s="73"/>
-      <c r="D24" s="348" t="s">
-        <v>196</v>
-      </c>
-      <c r="E24" s="349"/>
-      <c r="F24" s="349"/>
-      <c r="G24" s="349"/>
-      <c r="H24" s="348">
+      <c r="D24" s="354" t="s">
+        <v>185</v>
+      </c>
+      <c r="E24" s="355"/>
+      <c r="F24" s="355"/>
+      <c r="G24" s="355"/>
+      <c r="H24" s="354">
         <f>Assumptions.1!I12</f>
         <v>0</v>
       </c>
-      <c r="I24" s="349"/>
-      <c r="J24" s="349"/>
-      <c r="K24" s="248"/>
+      <c r="I24" s="355"/>
+      <c r="J24" s="355"/>
+      <c r="K24" s="246"/>
       <c r="L24" s="74"/>
     </row>
-    <row r="25" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B25" s="72"/>
       <c r="C25" s="73"/>
       <c r="E25" s="65"/>
@@ -9983,7 +9936,7 @@
       <c r="K25" s="73"/>
       <c r="L25" s="76"/>
     </row>
-    <row r="26" spans="2:12" ht="23.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="26" spans="2:23" ht="23.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B26" s="72"/>
       <c r="C26" s="73"/>
       <c r="E26" s="67"/>
@@ -9994,27 +9947,27 @@
       <c r="K26" s="73"/>
       <c r="L26" s="74"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B27" s="72"/>
       <c r="C27" s="73"/>
       <c r="K27" s="73"/>
       <c r="L27" s="74"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B28" s="72"/>
       <c r="C28" s="73"/>
-      <c r="E28" s="353" t="s">
-        <v>197</v>
-      </c>
-      <c r="F28" s="349"/>
-      <c r="G28" s="349"/>
-      <c r="H28" s="349"/>
-      <c r="I28" s="349"/>
+      <c r="E28" s="356" t="s">
+        <v>186</v>
+      </c>
+      <c r="F28" s="355"/>
+      <c r="G28" s="355"/>
+      <c r="H28" s="355"/>
+      <c r="I28" s="355"/>
       <c r="J28" s="68"/>
-      <c r="K28" s="249"/>
+      <c r="K28" s="247"/>
       <c r="L28" s="74"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B29" s="72"/>
       <c r="C29" s="73"/>
       <c r="E29" s="65"/>
@@ -10023,52 +9976,52 @@
       <c r="H29" s="65"/>
       <c r="I29" s="65"/>
       <c r="J29" s="65"/>
-      <c r="K29" s="250"/>
+      <c r="K29" s="248"/>
       <c r="L29" s="74"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B30" s="72"/>
       <c r="C30" s="73"/>
-      <c r="D30" s="348" t="s">
-        <v>198</v>
-      </c>
-      <c r="E30" s="349"/>
-      <c r="F30" s="349"/>
-      <c r="G30" s="349"/>
-      <c r="H30" s="349"/>
-      <c r="I30" s="349"/>
-      <c r="J30" s="349"/>
-      <c r="K30" s="248"/>
+      <c r="D30" s="354" t="s">
+        <v>187</v>
+      </c>
+      <c r="E30" s="355"/>
+      <c r="F30" s="355"/>
+      <c r="G30" s="355"/>
+      <c r="H30" s="355"/>
+      <c r="I30" s="355"/>
+      <c r="J30" s="355"/>
+      <c r="K30" s="246"/>
       <c r="L30" s="74"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B31" s="72"/>
       <c r="C31" s="73"/>
-      <c r="D31" s="348" t="s">
-        <v>199</v>
-      </c>
-      <c r="E31" s="349"/>
-      <c r="F31" s="349"/>
-      <c r="G31" s="349"/>
-      <c r="H31" s="349"/>
-      <c r="I31" s="349"/>
-      <c r="J31" s="349"/>
-      <c r="K31" s="248"/>
+      <c r="D31" s="354" t="s">
+        <v>188</v>
+      </c>
+      <c r="E31" s="355"/>
+      <c r="F31" s="355"/>
+      <c r="G31" s="355"/>
+      <c r="H31" s="355"/>
+      <c r="I31" s="355"/>
+      <c r="J31" s="355"/>
+      <c r="K31" s="246"/>
       <c r="L31" s="74"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B32" s="72"/>
       <c r="C32" s="73"/>
-      <c r="D32" s="348" t="s">
-        <v>200</v>
-      </c>
-      <c r="E32" s="349"/>
-      <c r="F32" s="349"/>
-      <c r="G32" s="349"/>
-      <c r="H32" s="349"/>
-      <c r="I32" s="349"/>
-      <c r="J32" s="349"/>
-      <c r="K32" s="248"/>
+      <c r="D32" s="354" t="s">
+        <v>189</v>
+      </c>
+      <c r="E32" s="355"/>
+      <c r="F32" s="355"/>
+      <c r="G32" s="355"/>
+      <c r="H32" s="355"/>
+      <c r="I32" s="355"/>
+      <c r="J32" s="355"/>
+      <c r="K32" s="246"/>
       <c r="L32" s="74"/>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.45">
@@ -10081,7 +10034,7 @@
       <c r="H33" s="64"/>
       <c r="I33" s="64"/>
       <c r="J33" s="64"/>
-      <c r="K33" s="248"/>
+      <c r="K33" s="246"/>
       <c r="L33" s="74"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.45">
@@ -10118,12 +10071,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="D31:J31"/>
-    <mergeCell ref="D32:J32"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="E28:I28"/>
     <mergeCell ref="D6:J6"/>
     <mergeCell ref="D24:G24"/>
     <mergeCell ref="E23:F23"/>
@@ -10131,6 +10078,12 @@
     <mergeCell ref="D30:J30"/>
     <mergeCell ref="E8:I8"/>
     <mergeCell ref="D16:J19"/>
+    <mergeCell ref="D31:J31"/>
+    <mergeCell ref="D32:J32"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="E28:I28"/>
   </mergeCells>
   <pageMargins left="0.21" right="0.24" top="0.35433070866141742" bottom="0.31496062992125978" header="0.19685039370078741" footer="0.15748031496062989"/>
   <pageSetup scale="92" orientation="portrait" r:id="rId1"/>
@@ -10151,58 +10104,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A1" s="345">
+      <c r="A1" s="339">
         <f>Assumptions.1!I4</f>
         <v>0</v>
       </c>
-      <c r="B1" s="346"/>
-      <c r="C1" s="346"/>
-      <c r="D1" s="346"/>
-      <c r="E1" s="346"/>
-      <c r="F1" s="346"/>
-      <c r="G1" s="346"/>
+      <c r="B1" s="340"/>
+      <c r="C1" s="340"/>
+      <c r="D1" s="340"/>
+      <c r="E1" s="340"/>
+      <c r="F1" s="340"/>
+      <c r="G1" s="340"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A2" s="345">
+      <c r="A2" s="339">
         <f>Assumptions.1!I6</f>
         <v>0</v>
       </c>
-      <c r="B2" s="346"/>
-      <c r="C2" s="346"/>
-      <c r="D2" s="346"/>
-      <c r="E2" s="346"/>
-      <c r="F2" s="346"/>
-      <c r="G2" s="346"/>
+      <c r="B2" s="340"/>
+      <c r="C2" s="340"/>
+      <c r="D2" s="340"/>
+      <c r="E2" s="340"/>
+      <c r="F2" s="340"/>
+      <c r="G2" s="340"/>
     </row>
     <row r="3" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="345">
+      <c r="A3" s="339">
         <f>Assumptions.1!I7</f>
         <v>0</v>
       </c>
-      <c r="B3" s="346"/>
-      <c r="C3" s="346"/>
-      <c r="D3" s="346"/>
-      <c r="E3" s="346"/>
-      <c r="F3" s="346"/>
-      <c r="G3" s="346"/>
+      <c r="B3" s="340"/>
+      <c r="C3" s="340"/>
+      <c r="D3" s="340"/>
+      <c r="E3" s="340"/>
+      <c r="F3" s="340"/>
+      <c r="G3" s="340"/>
     </row>
     <row r="4" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="354" t="s">
-        <v>201</v>
-      </c>
-      <c r="B4" s="328"/>
-      <c r="C4" s="328"/>
-      <c r="D4" s="328"/>
-      <c r="E4" s="328"/>
-      <c r="F4" s="328"/>
-      <c r="G4" s="328"/>
+      <c r="A4" s="360" t="s">
+        <v>190</v>
+      </c>
+      <c r="B4" s="335"/>
+      <c r="C4" s="335"/>
+      <c r="D4" s="335"/>
+      <c r="E4" s="335"/>
+      <c r="F4" s="335"/>
+      <c r="G4" s="335"/>
     </row>
     <row r="5" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="341" t="s">
+      <c r="A5" s="350" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" s="341" t="s">
         <v>122</v>
-      </c>
-      <c r="B5" s="339" t="s">
-        <v>123</v>
       </c>
       <c r="C5" s="100" t="str">
         <f>Assumptions.1!J17</f>
@@ -10226,8 +10179,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" s="3" customFormat="1" ht="75.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="340"/>
-      <c r="B6" s="340"/>
+      <c r="A6" s="342"/>
+      <c r="B6" s="342"/>
       <c r="C6" s="149">
         <f>Assumptions.1!I17</f>
         <v>0</v>
@@ -10256,7 +10209,7 @@
     </row>
     <row r="8" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A8" s="5" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -10268,7 +10221,7 @@
     </row>
     <row r="10" spans="1:7" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="2" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="B10" s="108"/>
       <c r="C10" s="6" t="e">
@@ -10326,7 +10279,7 @@
     <row r="13" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.5"/>
     <row r="14" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A14" s="5" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.5">
@@ -10334,7 +10287,7 @@
     </row>
     <row r="16" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C16" s="6">
         <f>Assumptions.1!F77</f>
@@ -10359,7 +10312,7 @@
     </row>
     <row r="17" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B17" s="108"/>
       <c r="C17" s="6" t="e">
@@ -10385,7 +10338,7 @@
     </row>
     <row r="18" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A18" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C18" s="6">
         <f>ROUND(FinalWorkings!C11,-3)</f>
@@ -10412,7 +10365,7 @@
     </row>
     <row r="19" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A19" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C19" s="7" t="e">
         <f>C16+C17-C18</f>
@@ -10440,7 +10393,7 @@
     </row>
     <row r="21" spans="1:13" s="3" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="5" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="C21" s="7" t="e">
         <f>C12-C19</f>
@@ -10473,7 +10426,7 @@
     </row>
     <row r="23" spans="1:13" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A23" s="2" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="B23" s="108"/>
       <c r="C23" s="7" t="e">
@@ -10507,10 +10460,10 @@
     </row>
     <row r="25" spans="1:13" ht="38.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A25" s="2" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="B25" s="108" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="C25" s="6" t="e">
         <f>C86</f>
@@ -10548,7 +10501,7 @@
     </row>
     <row r="27" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A27" s="5" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="15" t="e">
@@ -10588,7 +10541,7 @@
     </row>
     <row r="29" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A29" s="2" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="6">
@@ -10632,7 +10585,7 @@
     </row>
     <row r="31" spans="1:13" s="16" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A31" s="5" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="C31" s="15" t="e">
         <f>C27-C29</f>
@@ -10675,7 +10628,7 @@
     </row>
     <row r="33" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A33" s="2" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="6">
@@ -10713,7 +10666,7 @@
     </row>
     <row r="35" spans="1:13" s="3" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A35" s="8" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="B35" s="9"/>
       <c r="C35" s="14" t="e">
@@ -10756,40 +10709,40 @@
       <c r="G37" s="12"/>
     </row>
     <row r="38" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A38" s="355">
+      <c r="A38" s="361">
         <f>A1</f>
         <v>0</v>
       </c>
-      <c r="B38" s="356"/>
-      <c r="C38" s="356"/>
-      <c r="D38" s="356"/>
-      <c r="E38" s="356"/>
-      <c r="F38" s="356"/>
-      <c r="G38" s="356"/>
+      <c r="B38" s="362"/>
+      <c r="C38" s="362"/>
+      <c r="D38" s="362"/>
+      <c r="E38" s="362"/>
+      <c r="F38" s="362"/>
+      <c r="G38" s="362"/>
     </row>
     <row r="39" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A39" s="345">
+      <c r="A39" s="339">
         <f>A2</f>
         <v>0</v>
       </c>
-      <c r="B39" s="346"/>
-      <c r="C39" s="346"/>
-      <c r="D39" s="346"/>
-      <c r="E39" s="346"/>
-      <c r="F39" s="346"/>
-      <c r="G39" s="346"/>
+      <c r="B39" s="340"/>
+      <c r="C39" s="340"/>
+      <c r="D39" s="340"/>
+      <c r="E39" s="340"/>
+      <c r="F39" s="340"/>
+      <c r="G39" s="340"/>
     </row>
     <row r="40" spans="1:13" ht="44.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A40" s="345">
+      <c r="A40" s="339">
         <f>A3</f>
         <v>0</v>
       </c>
-      <c r="B40" s="346"/>
-      <c r="C40" s="346"/>
-      <c r="D40" s="346"/>
-      <c r="E40" s="346"/>
-      <c r="F40" s="346"/>
-      <c r="G40" s="346"/>
+      <c r="B40" s="340"/>
+      <c r="C40" s="340"/>
+      <c r="D40" s="340"/>
+      <c r="E40" s="340"/>
+      <c r="F40" s="340"/>
+      <c r="G40" s="340"/>
     </row>
     <row r="41" spans="1:13" ht="44.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A41" s="1"/>
@@ -10801,22 +10754,22 @@
       <c r="G41" s="1"/>
     </row>
     <row r="42" spans="1:13" ht="48.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A42" s="354" t="s">
-        <v>214</v>
-      </c>
-      <c r="B42" s="328"/>
-      <c r="C42" s="328"/>
-      <c r="D42" s="328"/>
-      <c r="E42" s="328"/>
-      <c r="F42" s="328"/>
-      <c r="G42" s="328"/>
+      <c r="A42" s="360" t="s">
+        <v>203</v>
+      </c>
+      <c r="B42" s="335"/>
+      <c r="C42" s="335"/>
+      <c r="D42" s="335"/>
+      <c r="E42" s="335"/>
+      <c r="F42" s="335"/>
+      <c r="G42" s="335"/>
     </row>
     <row r="43" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A43" s="339" t="s">
-        <v>138</v>
-      </c>
-      <c r="B43" s="339" t="s">
-        <v>123</v>
+      <c r="A43" s="341" t="s">
+        <v>137</v>
+      </c>
+      <c r="B43" s="341" t="s">
+        <v>122</v>
       </c>
       <c r="C43" s="102" t="str">
         <f>C5</f>
@@ -10840,8 +10793,8 @@
       </c>
     </row>
     <row r="44" spans="1:13" ht="95.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="340"/>
-      <c r="B44" s="340"/>
+      <c r="A44" s="342"/>
+      <c r="B44" s="342"/>
       <c r="C44" s="118">
         <f>C6</f>
         <v>0</v>
@@ -10865,7 +10818,7 @@
     </row>
     <row r="45" spans="1:13" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.5">
       <c r="A45" s="41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.5">
@@ -10873,7 +10826,7 @@
     </row>
     <row r="47" spans="1:13" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A47" s="2" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="B47" s="108"/>
       <c r="C47" s="48" t="e">
@@ -10902,21 +10855,21 @@
     </row>
     <row r="48" spans="1:13" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A48" s="50" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B48" s="10"/>
     </row>
     <row r="49" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.5"/>
     <row r="50" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A50" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B50" s="1"/>
       <c r="I50" s="106"/>
     </row>
     <row r="51" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A51" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B51" s="10"/>
       <c r="C51" s="46" t="e">
@@ -11005,7 +10958,7 @@
     <row r="56" spans="1:9" ht="25.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.5"/>
     <row r="59" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A59" s="41" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.5">
@@ -11013,7 +10966,7 @@
     </row>
     <row r="61" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A61" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C61" s="6">
         <f>Depsch!N18</f>
@@ -11079,7 +11032,7 @@
     </row>
     <row r="65" spans="1:15" ht="42.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A65" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B65" s="10"/>
       <c r="I65" s="106"/>
@@ -11120,7 +11073,7 @@
     </row>
     <row r="67" spans="1:15" ht="44.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A67" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B67" s="108"/>
       <c r="C67" s="6" t="e">
@@ -11148,7 +11101,7 @@
     </row>
     <row r="68" spans="1:15" ht="44.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A68" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B68" s="108"/>
       <c r="C68" s="6">
@@ -11176,7 +11129,7 @@
     </row>
     <row r="69" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A69" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B69" s="108"/>
       <c r="C69" s="6" t="e">
@@ -11257,15 +11210,15 @@
       <c r="M73" s="84"/>
     </row>
     <row r="74" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A74" s="354" t="s">
-        <v>216</v>
-      </c>
-      <c r="B74" s="328"/>
-      <c r="C74" s="328"/>
-      <c r="D74" s="328"/>
-      <c r="E74" s="328"/>
-      <c r="F74" s="328"/>
-      <c r="G74" s="328"/>
+      <c r="A74" s="360" t="s">
+        <v>205</v>
+      </c>
+      <c r="B74" s="335"/>
+      <c r="C74" s="335"/>
+      <c r="D74" s="335"/>
+      <c r="E74" s="335"/>
+      <c r="F74" s="335"/>
+      <c r="G74" s="335"/>
     </row>
     <row r="75" spans="1:15" ht="95.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="51"/>
@@ -11294,7 +11247,7 @@
     <row r="76" spans="1:15" ht="25.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.5"/>
     <row r="77" spans="1:15" x14ac:dyDescent="0.5">
       <c r="A77" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B77" s="108"/>
       <c r="C77" s="6">
@@ -11321,7 +11274,7 @@
     </row>
     <row r="78" spans="1:15" ht="35.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A78" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B78" s="108"/>
       <c r="C78" s="6">
@@ -11347,7 +11300,7 @@
     </row>
     <row r="79" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A79" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B79" s="108"/>
       <c r="C79" s="6">
@@ -11373,7 +11326,7 @@
     </row>
     <row r="80" spans="1:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A80" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B80" s="108"/>
       <c r="C80" s="6">
@@ -11399,7 +11352,7 @@
     </row>
     <row r="81" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A81" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B81" s="108"/>
       <c r="C81" s="6" t="e">
@@ -11425,7 +11378,7 @@
     </row>
     <row r="82" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A82" s="2" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="B82" s="108"/>
       <c r="C82" s="6" t="e">
@@ -11546,51 +11499,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="358">
+      <c r="A1" s="364">
         <f>Assumptions.1!I4</f>
         <v>0</v>
       </c>
-      <c r="B1" s="359"/>
-      <c r="C1" s="359"/>
-      <c r="D1" s="359"/>
-      <c r="E1" s="359"/>
-      <c r="F1" s="359"/>
-      <c r="G1" s="359"/>
+      <c r="B1" s="365"/>
+      <c r="C1" s="365"/>
+      <c r="D1" s="365"/>
+      <c r="E1" s="365"/>
+      <c r="F1" s="365"/>
+      <c r="G1" s="365"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="358">
+      <c r="A2" s="364">
         <f>Assumptions.1!I6</f>
         <v>0</v>
       </c>
-      <c r="B2" s="359"/>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
+      <c r="B2" s="365"/>
+      <c r="C2" s="365"/>
+      <c r="D2" s="365"/>
+      <c r="E2" s="365"/>
+      <c r="F2" s="365"/>
+      <c r="G2" s="365"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="358">
+      <c r="A3" s="364">
         <f>Assumptions.1!I7</f>
         <v>0</v>
       </c>
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
+      <c r="B3" s="365"/>
+      <c r="C3" s="365"/>
+      <c r="D3" s="365"/>
+      <c r="E3" s="365"/>
+      <c r="F3" s="365"/>
+      <c r="G3" s="365"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="365" t="s">
-        <v>218</v>
-      </c>
-      <c r="B5" s="359"/>
-      <c r="C5" s="359"/>
-      <c r="D5" s="359"/>
-      <c r="E5" s="359"/>
-      <c r="F5" s="359"/>
-      <c r="G5" s="359"/>
+      <c r="A5" s="371" t="s">
+        <v>207</v>
+      </c>
+      <c r="B5" s="365"/>
+      <c r="C5" s="365"/>
+      <c r="D5" s="365"/>
+      <c r="E5" s="365"/>
+      <c r="F5" s="365"/>
+      <c r="G5" s="365"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="17"/>
@@ -11601,8 +11554,8 @@
       <c r="F6" s="17"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="252" t="s">
-        <v>219</v>
+      <c r="A7" s="250" t="s">
+        <v>208</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
@@ -11610,17 +11563,17 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="30"/>
-      <c r="C8" s="363" t="s">
-        <v>220</v>
-      </c>
-      <c r="D8" s="328"/>
-      <c r="E8" s="328"/>
-      <c r="F8" s="328"/>
-      <c r="G8" s="328"/>
+      <c r="C8" s="369" t="s">
+        <v>209</v>
+      </c>
+      <c r="D8" s="335"/>
+      <c r="E8" s="335"/>
+      <c r="F8" s="335"/>
+      <c r="G8" s="335"/>
     </row>
     <row r="9" spans="1:7" ht="27.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="56" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B9" s="54"/>
       <c r="C9" s="120">
@@ -11649,7 +11602,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="18" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="C11" s="26" t="str">
         <f>IFERROR(C13/C14, "N/A")</f>
@@ -11678,7 +11631,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="18" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="C13" s="31" t="e">
         <f>SUM(plbs!C66:C70)</f>
@@ -11703,7 +11656,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="18" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="C14" s="31" t="e">
         <f>SUM(plbs!C51:C54)</f>
@@ -11750,7 +11703,7 @@
     </row>
     <row r="16" spans="1:7" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="21" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="21"/>
@@ -11768,13 +11721,13 @@
       <c r="F17" s="17"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="253" t="s">
-        <v>225</v>
+      <c r="A18" s="251" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="27.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="56" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B19" s="54"/>
       <c r="C19" s="120">
@@ -11806,7 +11759,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="18" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="C21" s="26" t="str">
         <f>IFERROR(plbs!C10/plbs!C67, "N/A")</f>
@@ -11830,63 +11783,63 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="364" t="s">
-        <v>227</v>
-      </c>
-      <c r="B22" s="359"/>
+      <c r="A22" s="370" t="s">
+        <v>216</v>
+      </c>
+      <c r="B22" s="365"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="360" t="s">
-        <v>228</v>
-      </c>
-      <c r="B24" s="359"/>
-      <c r="C24" s="359"/>
-      <c r="D24" s="359"/>
-      <c r="E24" s="359"/>
-      <c r="F24" s="359"/>
-      <c r="G24" s="359"/>
-      <c r="H24" s="359"/>
+      <c r="A24" s="366" t="s">
+        <v>217</v>
+      </c>
+      <c r="B24" s="365"/>
+      <c r="C24" s="365"/>
+      <c r="D24" s="365"/>
+      <c r="E24" s="365"/>
+      <c r="F24" s="365"/>
+      <c r="G24" s="365"/>
+      <c r="H24" s="365"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="18" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="294" t="s">
-        <v>230</v>
+      <c r="A27" s="292" t="s">
+        <v>219</v>
       </c>
       <c r="B27" s="27"/>
-      <c r="C27" s="295" t="str">
+      <c r="C27" s="293" t="str">
         <f>IFERROR(B30/C21, "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="D27" s="295" t="str">
+      <c r="D27" s="293" t="str">
         <f>IFERROR(B30/D21, "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="E27" s="295" t="str">
+      <c r="E27" s="293" t="str">
         <f>IFERROR(B30/E21, "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="F27" s="295" t="str">
+      <c r="F27" s="293" t="str">
         <f>IFERROR(B30/F21, "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="G27" s="295" t="str">
+      <c r="G27" s="293" t="str">
         <f>IFERROR(B30/G21, "N/A")</f>
         <v>N/A</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="360" t="s">
-        <v>231</v>
-      </c>
-      <c r="B28" s="359"/>
+      <c r="A28" s="366" t="s">
+        <v>220</v>
+      </c>
+      <c r="B28" s="365"/>
     </row>
     <row r="30" spans="1:8" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="28" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="B30" s="29">
         <v>365</v>
@@ -11906,8 +11859,8 @@
       <c r="F31" s="17"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" s="252" t="s">
-        <v>233</v>
+      <c r="A32" s="250" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
@@ -11915,7 +11868,7 @@
     </row>
     <row r="34" spans="1:7" ht="27.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="56" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B34" s="54"/>
       <c r="C34" s="120">
@@ -11941,7 +11894,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="18" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C36" s="26" t="str">
         <f>IFERROR(plbs!C21/plbs!C12*100, "N/A")</f>
@@ -11970,7 +11923,7 @@
     </row>
     <row r="38" spans="1:7" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="32" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="B38" s="21"/>
       <c r="C38" s="21"/>
@@ -11983,8 +11936,8 @@
       <c r="D39" s="33"/>
     </row>
     <row r="40" spans="1:7" ht="15.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="252" t="s">
-        <v>236</v>
+      <c r="A40" s="250" t="s">
+        <v>225</v>
       </c>
       <c r="D40" s="33"/>
     </row>
@@ -11994,7 +11947,7 @@
     </row>
     <row r="42" spans="1:7" ht="27.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="56" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B42" s="54"/>
       <c r="C42" s="120">
@@ -12023,7 +11976,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="18" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="C44" s="26" t="str">
         <f>IFERROR(plbs!C35/plbs!C12*100, "N/A")</f>
@@ -12052,7 +12005,7 @@
     </row>
     <row r="46" spans="1:7" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="32" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
@@ -12070,21 +12023,21 @@
       <c r="F47" s="17"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A48" s="252" t="s">
-        <v>239</v>
+      <c r="A48" s="250" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="D49" s="362" t="s">
-        <v>240</v>
-      </c>
-      <c r="E49" s="328"/>
-      <c r="F49" s="328"/>
-      <c r="G49" s="328"/>
+      <c r="D49" s="368" t="s">
+        <v>229</v>
+      </c>
+      <c r="E49" s="335"/>
+      <c r="F49" s="335"/>
+      <c r="G49" s="335"/>
     </row>
     <row r="50" spans="1:7" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="53" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="B50" s="54"/>
       <c r="C50" s="120">
@@ -12110,7 +12063,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="18" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="C52" s="26" t="str">
         <f>IFERROR(C54/C55, "N/A")</f>
@@ -12142,7 +12095,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="18" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="C54" s="31" t="e">
         <f>plbs!C31</f>
@@ -12167,7 +12120,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="18" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="C55" s="31">
         <f>plbs!C33</f>
@@ -12196,7 +12149,7 @@
     </row>
     <row r="57" spans="1:7" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="21" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="B57" s="21"/>
       <c r="C57" s="21"/>
@@ -12224,8 +12177,8 @@
       <c r="G59" s="17"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A60" s="253" t="s">
-        <v>246</v>
+      <c r="A60" s="251" t="s">
+        <v>235</v>
       </c>
       <c r="B60" s="43"/>
       <c r="C60" s="17"/>
@@ -12239,7 +12192,7 @@
     </row>
     <row r="62" spans="1:7" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="53" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B62" s="57"/>
       <c r="C62" s="120">
@@ -12271,7 +12224,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="18" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="B64" s="17"/>
       <c r="C64" s="45" t="e">
@@ -12302,7 +12255,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="23" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="B66" s="17"/>
       <c r="C66" s="19" t="e">
@@ -12333,10 +12286,10 @@
       <c r="D67" s="17"/>
     </row>
     <row r="68" spans="1:7" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="361" t="s">
-        <v>249</v>
-      </c>
-      <c r="B68" s="343"/>
+      <c r="A68" s="367" t="s">
+        <v>238</v>
+      </c>
+      <c r="B68" s="344"/>
       <c r="C68" s="20"/>
       <c r="D68" s="20"/>
       <c r="E68" s="21"/>
@@ -12350,8 +12303,8 @@
       <c r="D69" s="17"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A70" s="253" t="s">
-        <v>250</v>
+      <c r="A70" s="251" t="s">
+        <v>239</v>
       </c>
       <c r="B70" s="17"/>
       <c r="C70" s="17"/>
@@ -12365,7 +12318,7 @@
     </row>
     <row r="72" spans="1:7" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="56" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B72" s="58"/>
       <c r="C72" s="120">
@@ -12396,7 +12349,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="44" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="C74" s="31" t="e">
         <f>plbs!C19</f>
@@ -12421,7 +12374,7 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="18" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="C75" s="18">
         <f>(plbs!C16+plbs!C18)/2</f>
@@ -12446,7 +12399,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="18" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="C76" s="26" t="e">
         <f>C74/C75</f>
@@ -12472,21 +12425,21 @@
     <row r="77" spans="1:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="78" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="18" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="18" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="357" t="s">
-        <v>256</v>
-      </c>
-      <c r="B80" s="343"/>
-      <c r="C80" s="343"/>
-      <c r="D80" s="343"/>
+      <c r="A80" s="363" t="s">
+        <v>245</v>
+      </c>
+      <c r="B80" s="344"/>
+      <c r="C80" s="344"/>
+      <c r="D80" s="344"/>
       <c r="E80" s="21"/>
       <c r="F80" s="21"/>
       <c r="G80" s="21"/>
@@ -12498,8 +12451,8 @@
       <c r="D81" s="23"/>
     </row>
     <row r="83" spans="1:7" ht="15.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="252" t="s">
-        <v>257</v>
+      <c r="A83" s="250" t="s">
+        <v>246</v>
       </c>
       <c r="D83" s="33"/>
     </row>
@@ -12509,7 +12462,7 @@
     </row>
     <row r="85" spans="1:7" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="56" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B85" s="54"/>
       <c r="C85" s="120">
@@ -12538,7 +12491,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="18" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="C87" s="26" t="e">
         <f>SUM(plbs!C49:C54)/plbs!C47</f>
@@ -12567,7 +12520,7 @@
     </row>
     <row r="89" spans="1:7" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="21" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="B89" s="21"/>
       <c r="C89" s="21"/>
@@ -12580,13 +12533,13 @@
       <c r="D90" s="33"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A91" s="252" t="s">
-        <v>260</v>
+      <c r="A91" s="250" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="53" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B93" s="54"/>
       <c r="C93" s="120">
@@ -12612,7 +12565,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="18" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="C95" s="26" t="e">
         <f>plbs!C35/(plbs!C47+plbs!C48+plbs!C49)</f>
@@ -12637,7 +12590,7 @@
     </row>
     <row r="97" spans="1:7" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="21" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="B97" s="21"/>
       <c r="C97" s="21"/>
@@ -12686,56 +12639,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="366">
+      <c r="A1" s="372">
         <f>Assumptions.1!I4</f>
         <v>0</v>
       </c>
-      <c r="B1" s="367"/>
-      <c r="C1" s="367"/>
-      <c r="D1" s="367"/>
-      <c r="E1" s="367"/>
-      <c r="F1" s="367"/>
+      <c r="B1" s="373"/>
+      <c r="C1" s="373"/>
+      <c r="D1" s="373"/>
+      <c r="E1" s="373"/>
+      <c r="F1" s="373"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="366">
+      <c r="A2" s="372">
         <f>Assumptions.1!I6</f>
         <v>0</v>
       </c>
-      <c r="B2" s="367"/>
-      <c r="C2" s="367"/>
-      <c r="D2" s="367"/>
-      <c r="E2" s="367"/>
-      <c r="F2" s="367"/>
+      <c r="B2" s="373"/>
+      <c r="C2" s="373"/>
+      <c r="D2" s="373"/>
+      <c r="E2" s="373"/>
+      <c r="F2" s="373"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="366">
+      <c r="A3" s="372">
         <f>Assumptions.1!I7</f>
         <v>0</v>
       </c>
-      <c r="B3" s="367"/>
-      <c r="C3" s="367"/>
-      <c r="D3" s="367"/>
-      <c r="E3" s="367"/>
-      <c r="F3" s="367"/>
+      <c r="B3" s="373"/>
+      <c r="C3" s="373"/>
+      <c r="D3" s="373"/>
+      <c r="E3" s="373"/>
+      <c r="F3" s="373"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="368" t="s">
-        <v>263</v>
-      </c>
-      <c r="B5" s="367"/>
-      <c r="C5" s="367"/>
-      <c r="D5" s="367"/>
-      <c r="E5" s="367"/>
-      <c r="F5" s="367"/>
+      <c r="A5" s="374" t="s">
+        <v>252</v>
+      </c>
+      <c r="B5" s="373"/>
+      <c r="C5" s="373"/>
+      <c r="D5" s="373"/>
+      <c r="E5" s="373"/>
+      <c r="F5" s="373"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="38" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="59" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B8" s="121">
         <f>wc!C6</f>
@@ -12767,7 +12720,7 @@
     </row>
     <row r="10" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="36" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="B10" s="40" t="e">
         <f>SUM(plbs!C65:C70)</f>
@@ -12799,7 +12752,7 @@
     </row>
     <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="36" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="B12" s="40">
         <f>plbs!C52+plbs!C53+plbs!C54</f>
@@ -12824,13 +12777,13 @@
     </row>
     <row r="13" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="36" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="36" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="B15" s="40" t="e">
         <f>+B10-B12</f>
@@ -12862,12 +12815,12 @@
     </row>
     <row r="17" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="36" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="36" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="B18" s="40" t="e">
         <f>+B15*0.25</f>
@@ -12892,12 +12845,12 @@
     </row>
     <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="36" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="36" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="B21" s="40" t="e">
         <f>RATIO!C15</f>
@@ -12929,7 +12882,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="36" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="B23" s="40" t="e">
         <f>+B15-B18</f>
@@ -12961,7 +12914,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="36" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="B25" s="40" t="e">
         <f>B15-B21</f>
@@ -12993,7 +12946,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="37" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="B27" s="61" t="e">
         <f>IF(B23&lt;B25,B23,B25)</f>
@@ -13018,7 +12971,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="37" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="B28" s="37"/>
       <c r="C28" s="37"/>
@@ -13036,12 +12989,12 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="38" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="29.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="59" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B32" s="121">
         <f>B8</f>
@@ -13073,7 +13026,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="36" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="B34" s="40" t="e">
         <f>B10</f>
@@ -13105,7 +13058,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="36" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="B36" s="40">
         <f>B12</f>
@@ -13130,12 +13083,12 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="36" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="36" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="B39" s="40" t="e">
         <f>+B34-B36</f>
@@ -13167,12 +13120,12 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="36" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="36" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="B42" s="40" t="e">
         <f>25/100*B34</f>
@@ -13197,7 +13150,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="36" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="B44" s="40" t="e">
         <f>B21</f>
@@ -13229,7 +13182,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="36" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="B46" s="40" t="e">
         <f>+B39-B42</f>
@@ -13261,7 +13214,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="36" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="B48" s="40" t="e">
         <f>B39-B44</f>
@@ -13293,7 +13246,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="37" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="B50" s="61" t="e">
         <f>IF(B46&lt;B48,B46,B48)</f>
@@ -13318,7 +13271,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="37" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="B51" s="37"/>
       <c r="C51" s="37"/>
@@ -13362,70 +13315,70 @@
   <sheetData>
     <row r="1" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="366">
+      <c r="A2" s="372">
         <f>Assumptions.1!I4</f>
         <v>0</v>
       </c>
-      <c r="B2" s="367"/>
-      <c r="C2" s="367"/>
-      <c r="D2" s="367"/>
-      <c r="E2" s="367"/>
-      <c r="F2" s="367"/>
-      <c r="G2" s="367"/>
+      <c r="B2" s="373"/>
+      <c r="C2" s="373"/>
+      <c r="D2" s="373"/>
+      <c r="E2" s="373"/>
+      <c r="F2" s="373"/>
+      <c r="G2" s="373"/>
     </row>
     <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="366">
+      <c r="A3" s="372">
         <f>Assumptions.1!I6</f>
         <v>0</v>
       </c>
-      <c r="B3" s="367"/>
-      <c r="C3" s="367"/>
-      <c r="D3" s="367"/>
-      <c r="E3" s="367"/>
-      <c r="F3" s="367"/>
-      <c r="G3" s="367"/>
+      <c r="B3" s="373"/>
+      <c r="C3" s="373"/>
+      <c r="D3" s="373"/>
+      <c r="E3" s="373"/>
+      <c r="F3" s="373"/>
+      <c r="G3" s="373"/>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="366">
+      <c r="A4" s="372">
         <f>Assumptions.1!I7</f>
         <v>0</v>
       </c>
-      <c r="B4" s="367"/>
-      <c r="C4" s="367"/>
-      <c r="D4" s="367"/>
-      <c r="E4" s="367"/>
-      <c r="F4" s="367"/>
-      <c r="G4" s="367"/>
+      <c r="B4" s="373"/>
+      <c r="C4" s="373"/>
+      <c r="D4" s="373"/>
+      <c r="E4" s="373"/>
+      <c r="F4" s="373"/>
+      <c r="G4" s="373"/>
     </row>
     <row r="6" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="368" t="s">
-        <v>279</v>
-      </c>
-      <c r="B6" s="367"/>
-      <c r="C6" s="367"/>
-      <c r="D6" s="367"/>
-      <c r="E6" s="367"/>
-      <c r="F6" s="367"/>
-      <c r="G6" s="367"/>
+      <c r="A6" s="374" t="s">
+        <v>268</v>
+      </c>
+      <c r="B6" s="373"/>
+      <c r="C6" s="373"/>
+      <c r="D6" s="373"/>
+      <c r="E6" s="373"/>
+      <c r="F6" s="373"/>
+      <c r="G6" s="373"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="37"/>
       <c r="B7" s="37"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="366" t="s">
-        <v>280</v>
-      </c>
-      <c r="B8" s="367"/>
-      <c r="C8" s="367"/>
-      <c r="D8" s="367"/>
-      <c r="E8" s="367"/>
-      <c r="F8" s="367"/>
-      <c r="G8" s="367"/>
+      <c r="A8" s="372" t="s">
+        <v>269</v>
+      </c>
+      <c r="B8" s="373"/>
+      <c r="C8" s="373"/>
+      <c r="D8" s="373"/>
+      <c r="E8" s="373"/>
+      <c r="F8" s="373"/>
+      <c r="G8" s="373"/>
     </row>
     <row r="10" spans="1:7" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="62" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B10" s="63"/>
       <c r="C10" s="122">
@@ -13451,7 +13404,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="36" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="B12" s="40"/>
       <c r="C12" s="40" t="e">
@@ -13480,7 +13433,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="36" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="B14" s="40"/>
       <c r="C14" s="40" t="e">
@@ -13506,7 +13459,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="36" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="B15" s="40"/>
     </row>
@@ -13515,7 +13468,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="36" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="B17" s="40"/>
       <c r="C17" s="40" t="e">
@@ -13541,7 +13494,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="36" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="B18" s="40"/>
     </row>
@@ -13550,7 +13503,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="36" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="B20" s="40"/>
       <c r="C20" s="40">
@@ -13578,13 +13531,13 @@
       <c r="B21" s="40"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="369" t="s">
-        <v>287</v>
+      <c r="A22" s="375" t="s">
+        <v>276</v>
       </c>
       <c r="B22" s="40"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="367"/>
+      <c r="A23" s="373"/>
       <c r="B23" s="40"/>
       <c r="C23" s="40" t="e">
         <f>IF(C17&lt;C20,C17,C20)</f>
@@ -13618,17 +13571,17 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="37" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="36" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="36" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -13661,79 +13614,79 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A1" s="358">
+      <c r="A1" s="364">
         <f>Assumptions.1!I4</f>
         <v>0</v>
       </c>
-      <c r="B1" s="359"/>
-      <c r="C1" s="359"/>
-      <c r="D1" s="359"/>
-      <c r="E1" s="359"/>
-      <c r="F1" s="359"/>
-      <c r="G1" s="359"/>
-      <c r="H1" s="359"/>
-      <c r="I1" s="359"/>
-      <c r="J1" s="359"/>
-      <c r="K1" s="359"/>
-      <c r="L1" s="359"/>
-      <c r="M1" s="359"/>
-      <c r="N1" s="359"/>
+      <c r="B1" s="365"/>
+      <c r="C1" s="365"/>
+      <c r="D1" s="365"/>
+      <c r="E1" s="365"/>
+      <c r="F1" s="365"/>
+      <c r="G1" s="365"/>
+      <c r="H1" s="365"/>
+      <c r="I1" s="365"/>
+      <c r="J1" s="365"/>
+      <c r="K1" s="365"/>
+      <c r="L1" s="365"/>
+      <c r="M1" s="365"/>
+      <c r="N1" s="365"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="358">
+      <c r="A2" s="364">
         <f>Assumptions.1!I6</f>
         <v>0</v>
       </c>
-      <c r="B2" s="359"/>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
-      <c r="I2" s="359"/>
-      <c r="J2" s="359"/>
-      <c r="K2" s="359"/>
-      <c r="L2" s="359"/>
-      <c r="M2" s="359"/>
-      <c r="N2" s="359"/>
+      <c r="B2" s="365"/>
+      <c r="C2" s="365"/>
+      <c r="D2" s="365"/>
+      <c r="E2" s="365"/>
+      <c r="F2" s="365"/>
+      <c r="G2" s="365"/>
+      <c r="H2" s="365"/>
+      <c r="I2" s="365"/>
+      <c r="J2" s="365"/>
+      <c r="K2" s="365"/>
+      <c r="L2" s="365"/>
+      <c r="M2" s="365"/>
+      <c r="N2" s="365"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" s="358">
+      <c r="A3" s="364">
         <f>Assumptions.1!I7</f>
         <v>0</v>
       </c>
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
-      <c r="F3" s="359"/>
-      <c r="G3" s="359"/>
-      <c r="H3" s="359"/>
-      <c r="I3" s="359"/>
-      <c r="J3" s="359"/>
-      <c r="K3" s="359"/>
-      <c r="L3" s="359"/>
-      <c r="M3" s="359"/>
-      <c r="N3" s="359"/>
+      <c r="B3" s="365"/>
+      <c r="C3" s="365"/>
+      <c r="D3" s="365"/>
+      <c r="E3" s="365"/>
+      <c r="F3" s="365"/>
+      <c r="G3" s="365"/>
+      <c r="H3" s="365"/>
+      <c r="I3" s="365"/>
+      <c r="J3" s="365"/>
+      <c r="K3" s="365"/>
+      <c r="L3" s="365"/>
+      <c r="M3" s="365"/>
+      <c r="N3" s="365"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" s="358" t="s">
-        <v>291</v>
-      </c>
-      <c r="B5" s="359"/>
-      <c r="C5" s="359"/>
-      <c r="D5" s="359"/>
-      <c r="E5" s="359"/>
-      <c r="F5" s="359"/>
-      <c r="G5" s="359"/>
-      <c r="H5" s="359"/>
-      <c r="I5" s="359"/>
-      <c r="J5" s="359"/>
-      <c r="K5" s="359"/>
-      <c r="L5" s="359"/>
-      <c r="M5" s="359"/>
-      <c r="N5" s="359"/>
+      <c r="A5" s="364" t="s">
+        <v>280</v>
+      </c>
+      <c r="B5" s="365"/>
+      <c r="C5" s="365"/>
+      <c r="D5" s="365"/>
+      <c r="E5" s="365"/>
+      <c r="F5" s="365"/>
+      <c r="G5" s="365"/>
+      <c r="H5" s="365"/>
+      <c r="I5" s="365"/>
+      <c r="J5" s="365"/>
+      <c r="K5" s="365"/>
+      <c r="L5" s="365"/>
+      <c r="M5" s="365"/>
+      <c r="N5" s="365"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="86"/>
@@ -13753,53 +13706,53 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="N7" s="25" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="92"/>
       <c r="B8" s="93"/>
-      <c r="C8" s="371" t="str">
+      <c r="C8" s="377" t="str">
         <f>Assumptions.1!B99</f>
         <v>Plant and Machinery</v>
       </c>
-      <c r="D8" s="370" t="str">
+      <c r="D8" s="376" t="str">
         <f>Assumptions.1!B109</f>
         <v>Service Equipment</v>
       </c>
-      <c r="E8" s="370" t="str">
+      <c r="E8" s="376" t="str">
         <f>Assumptions.1!B119</f>
         <v>Shed and Civil works</v>
       </c>
-      <c r="F8" s="370" t="str">
+      <c r="F8" s="376" t="str">
         <f>Assumptions.1!B129</f>
         <v>Land</v>
       </c>
-      <c r="G8" s="370" t="str">
+      <c r="G8" s="376" t="str">
         <f>Assumptions.1!B132</f>
         <v>Electrical Items</v>
       </c>
-      <c r="H8" s="370" t="str">
+      <c r="H8" s="376" t="str">
         <f>Assumptions.1!B141</f>
         <v>Electronic items</v>
       </c>
-      <c r="I8" s="370" t="str">
+      <c r="I8" s="376" t="str">
         <f>Assumptions.1!B151</f>
         <v xml:space="preserve">Furniture and Fittings </v>
       </c>
-      <c r="J8" s="370" t="str">
+      <c r="J8" s="376" t="str">
         <f>Assumptions.1!B161</f>
         <v>Vehicles</v>
       </c>
-      <c r="K8" s="370" t="str">
+      <c r="K8" s="376" t="str">
         <f>Assumptions.1!B171</f>
         <v>Live stock</v>
       </c>
-      <c r="L8" s="370" t="str">
+      <c r="L8" s="376" t="str">
         <f>Assumptions.1!B180</f>
         <v>Other Assets</v>
       </c>
-      <c r="M8" s="370" t="str">
+      <c r="M8" s="376" t="str">
         <f>Assumptions.1!B190</f>
         <v>Other Assets (Nil Depreciation)</v>
       </c>
@@ -13808,19 +13761,19 @@
     <row r="9" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="94"/>
       <c r="B9" s="95"/>
-      <c r="C9" s="359"/>
-      <c r="D9" s="359"/>
-      <c r="E9" s="359"/>
-      <c r="F9" s="359"/>
-      <c r="G9" s="359"/>
-      <c r="H9" s="359"/>
-      <c r="I9" s="359"/>
-      <c r="J9" s="359"/>
-      <c r="K9" s="359"/>
-      <c r="L9" s="359"/>
-      <c r="M9" s="359"/>
+      <c r="C9" s="365"/>
+      <c r="D9" s="365"/>
+      <c r="E9" s="365"/>
+      <c r="F9" s="365"/>
+      <c r="G9" s="365"/>
+      <c r="H9" s="365"/>
+      <c r="I9" s="365"/>
+      <c r="J9" s="365"/>
+      <c r="K9" s="365"/>
+      <c r="L9" s="365"/>
+      <c r="M9" s="365"/>
       <c r="N9" s="95" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -13927,7 +13880,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="18" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="B14" s="87"/>
       <c r="C14" s="88">
@@ -13983,7 +13936,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="18" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="B15" s="87"/>
       <c r="C15" s="18">
@@ -14025,7 +13978,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="18" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="B16" s="87"/>
       <c r="C16" s="88">
@@ -14081,7 +14034,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B17" s="87"/>
       <c r="C17" s="88">
@@ -14137,7 +14090,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="18" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="B18" s="87"/>
       <c r="C18" s="88">
@@ -14231,7 +14184,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" s="18" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="B21" s="87"/>
       <c r="C21" s="88">
@@ -14287,7 +14240,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="18" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="B22" s="87"/>
       <c r="C22" s="88">
@@ -14332,7 +14285,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" s="18" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="B23" s="87"/>
       <c r="C23" s="88">
@@ -14388,7 +14341,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B24" s="87"/>
       <c r="C24" s="88">
@@ -14444,7 +14397,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="18" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="B25" s="87"/>
       <c r="C25" s="88">
@@ -14538,7 +14491,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" s="18" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="B28" s="87"/>
       <c r="C28" s="88">
@@ -14594,7 +14547,7 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" s="18" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="B29" s="87"/>
       <c r="C29" s="88">
@@ -14639,7 +14592,7 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="18" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="B30" s="87"/>
       <c r="C30" s="88">
@@ -14695,7 +14648,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B31" s="87"/>
       <c r="C31" s="88">
@@ -14751,7 +14704,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" s="18" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="B32" s="87"/>
       <c r="C32" s="88">
@@ -14844,7 +14797,7 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35" s="18" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="B35" s="87"/>
       <c r="C35" s="88">
@@ -14900,7 +14853,7 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36" s="18" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="B36" s="87"/>
       <c r="C36" s="88">
@@ -14945,7 +14898,7 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37" s="18" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="B37" s="87"/>
       <c r="C37" s="88">
@@ -15001,7 +14954,7 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A38" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B38" s="87"/>
       <c r="C38" s="88">
@@ -15057,7 +15010,7 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39" s="18" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="B39" s="87"/>
       <c r="C39" s="88">
@@ -15151,7 +15104,7 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A42" s="18" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="B42" s="87"/>
       <c r="C42" s="88">
@@ -15207,7 +15160,7 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43" s="18" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="B43" s="87"/>
       <c r="C43" s="88">
@@ -15252,7 +15205,7 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A44" s="18" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="B44" s="87"/>
       <c r="C44" s="88">
@@ -15308,7 +15261,7 @@
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A45" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B45" s="87"/>
       <c r="C45" s="88">
@@ -15364,7 +15317,7 @@
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46" s="18" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="B46" s="87"/>
       <c r="C46" s="88">
@@ -15420,19 +15373,19 @@
     </row>
     <row r="47" spans="1:16" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="21"/>
-      <c r="B47" s="297"/>
-      <c r="C47" s="298"/>
-      <c r="D47" s="298"/>
-      <c r="E47" s="298"/>
-      <c r="F47" s="298"/>
-      <c r="G47" s="298"/>
-      <c r="H47" s="298"/>
-      <c r="I47" s="298"/>
-      <c r="J47" s="298"/>
-      <c r="K47" s="298"/>
-      <c r="L47" s="298"/>
-      <c r="M47" s="298"/>
-      <c r="N47" s="299"/>
+      <c r="B47" s="295"/>
+      <c r="C47" s="296"/>
+      <c r="D47" s="296"/>
+      <c r="E47" s="296"/>
+      <c r="F47" s="296"/>
+      <c r="G47" s="296"/>
+      <c r="H47" s="296"/>
+      <c r="I47" s="296"/>
+      <c r="J47" s="296"/>
+      <c r="K47" s="296"/>
+      <c r="L47" s="296"/>
+      <c r="M47" s="296"/>
+      <c r="N47" s="297"/>
       <c r="O47" s="31"/>
       <c r="P47" s="31"/>
     </row>
